--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/html league/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{436B2CFE-4C32-4766-AD3B-9C0A59647518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09EE0B4A-4860-4308-AEB0-D6594FA20330}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D3AE3C8-6A28-43B3-8259-CAC9D66D9540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="450">
   <si>
     <t>Stage 1</t>
   </si>
@@ -1374,6 +1374,21 @@
   </si>
   <si>
     <t>Finlay Pickering</t>
+  </si>
+  <si>
+    <t>Xandro Meurisse</t>
+  </si>
+  <si>
+    <t>Marijn Van Den Berg</t>
+  </si>
+  <si>
+    <t>Mathieu Van Der Poel</t>
+  </si>
+  <si>
+    <t>Michael Matthews</t>
+  </si>
+  <si>
+    <t>Pau Miquel</t>
   </si>
 </sst>
 </file>
@@ -1752,17 +1767,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M115"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M116"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1803,7 +1818,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -1844,7 +1859,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1885,7 +1900,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1926,7 +1941,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1967,7 +1982,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2008,7 +2023,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2049,7 +2064,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2090,7 +2105,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2131,7 +2146,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2172,7 +2187,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2213,7 +2228,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2254,7 +2269,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2295,7 +2310,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2336,7 +2351,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2377,7 +2392,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2418,7 +2433,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2459,7 +2474,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -2500,7 +2515,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -2541,7 +2556,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -2582,7 +2597,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2623,7 +2638,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2664,7 +2679,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2705,7 +2720,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2746,7 +2761,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -2787,7 +2802,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -2828,7 +2843,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -2869,7 +2884,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -2910,7 +2925,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -2951,7 +2966,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -2992,7 +3007,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3033,7 +3048,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3074,7 +3089,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3115,7 +3130,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3156,7 +3171,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3197,7 +3212,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3238,7 +3253,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3279,7 +3294,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3320,7 +3335,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3361,7 +3376,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3402,7 +3417,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -3443,7 +3458,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -3484,7 +3499,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -3525,7 +3540,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -3566,7 +3581,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -3607,7 +3622,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -3648,7 +3663,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -3689,7 +3704,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -3730,7 +3745,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -3771,7 +3786,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -3812,7 +3827,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -3853,7 +3868,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -3894,7 +3909,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -3935,7 +3950,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -3976,7 +3991,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4017,7 +4032,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4058,7 +4073,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4099,7 +4114,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4140,7 +4155,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4181,7 +4196,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4222,7 +4237,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4263,7 +4278,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4304,7 +4319,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4345,7 +4360,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4386,7 +4401,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4427,7 +4442,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -4468,7 +4483,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -4509,7 +4524,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -4550,7 +4565,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -4591,7 +4606,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -4632,7 +4647,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -4673,7 +4688,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -4714,7 +4729,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -4755,7 +4770,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -4796,7 +4811,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -4837,7 +4852,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -4878,7 +4893,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -4919,7 +4934,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -4960,7 +4975,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5001,7 +5016,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5042,7 +5057,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5083,7 +5098,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5124,7 +5139,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5165,7 +5180,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5206,7 +5221,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5247,7 +5262,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5288,7 +5303,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5329,7 +5344,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5370,7 +5385,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5411,7 +5426,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -5452,7 +5467,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -5493,7 +5508,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -5534,7 +5549,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -5575,7 +5590,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -5616,7 +5631,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -5657,7 +5672,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -5698,7 +5713,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -5739,7 +5754,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -5780,7 +5795,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -5821,7 +5836,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -5862,7 +5877,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -5903,7 +5918,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -5944,7 +5959,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -5985,7 +6000,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6026,7 +6041,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6067,7 +6082,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6108,7 +6123,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6149,7 +6164,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6190,7 +6205,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6231,7 +6246,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6272,7 +6287,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6313,7 +6328,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6354,7 +6369,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6395,7 +6410,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6436,7 +6451,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -6475,6 +6490,47 @@
       </c>
       <c r="M115" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B116" t="s">
+        <v>441</v>
+      </c>
+      <c r="C116" t="s">
+        <v>43</v>
+      </c>
+      <c r="D116" t="s">
+        <v>26</v>
+      </c>
+      <c r="E116" t="s">
+        <v>445</v>
+      </c>
+      <c r="F116" t="s">
+        <v>86</v>
+      </c>
+      <c r="G116" t="s">
+        <v>446</v>
+      </c>
+      <c r="H116" t="s">
+        <v>447</v>
+      </c>
+      <c r="I116" t="s">
+        <v>257</v>
+      </c>
+      <c r="J116" t="s">
+        <v>299</v>
+      </c>
+      <c r="K116" t="s">
+        <v>448</v>
+      </c>
+      <c r="L116" t="s">
+        <v>449</v>
+      </c>
+      <c r="M116" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Desktop/Fantasy Cycling/html league/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{1D3AE3C8-6A28-43B3-8259-CAC9D66D9540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13529FC0-5827-4921-93A7-6460AA385E1A}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{1D3AE3C8-6A28-43B3-8259-CAC9D66D9540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67154B1C-75F9-4A4A-BF77-94E199B917A2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="454">
   <si>
     <t>Stage 1</t>
   </si>
@@ -1398,6 +1398,9 @@
   </si>
   <si>
     <t>Sander De Pestel</t>
+  </si>
+  <si>
+    <t>Tour de France</t>
   </si>
 </sst>
 </file>
@@ -1776,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -6622,6 +6625,47 @@
       </c>
       <c r="M118" t="s">
         <v>357</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B119" t="s">
+        <v>453</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1</v>
+      </c>
+      <c r="D119" t="s">
+        <v>433</v>
+      </c>
+      <c r="E119" t="s">
+        <v>204</v>
+      </c>
+      <c r="F119" t="s">
+        <v>74</v>
+      </c>
+      <c r="G119" t="s">
+        <v>221</v>
+      </c>
+      <c r="H119" t="s">
+        <v>182</v>
+      </c>
+      <c r="I119" t="s">
+        <v>106</v>
+      </c>
+      <c r="J119" t="s">
+        <v>190</v>
+      </c>
+      <c r="K119" t="s">
+        <v>180</v>
+      </c>
+      <c r="L119" t="s">
+        <v>142</v>
+      </c>
+      <c r="M119" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{1D3AE3C8-6A28-43B3-8259-CAC9D66D9540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67154B1C-75F9-4A4A-BF77-94E199B917A2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BA239DC-44EC-46E1-84DB-96F0DDA67AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="454">
   <si>
     <t>Stage 1</t>
   </si>
@@ -1779,17 +1779,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M119"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M120"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4413,7 +4413,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -4987,7 +4987,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -5561,7 +5561,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -5643,7 +5643,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -5766,7 +5766,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -5889,7 +5889,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -5930,7 +5930,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6053,7 +6053,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6217,7 +6217,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6299,7 +6299,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6381,7 +6381,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6463,7 +6463,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -6586,7 +6586,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -6627,7 +6627,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -6666,6 +6666,47 @@
       </c>
       <c r="M119" t="s">
         <v>344</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B120" t="s">
+        <v>453</v>
+      </c>
+      <c r="C120" t="s">
+        <v>43</v>
+      </c>
+      <c r="D120" t="s">
+        <v>204</v>
+      </c>
+      <c r="E120" t="s">
+        <v>221</v>
+      </c>
+      <c r="F120" t="s">
+        <v>282</v>
+      </c>
+      <c r="G120" t="s">
+        <v>142</v>
+      </c>
+      <c r="H120" t="s">
+        <v>106</v>
+      </c>
+      <c r="I120" t="s">
+        <v>105</v>
+      </c>
+      <c r="J120" t="s">
+        <v>157</v>
+      </c>
+      <c r="K120" t="s">
+        <v>74</v>
+      </c>
+      <c r="L120" t="s">
+        <v>433</v>
+      </c>
+      <c r="M120" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BA239DC-44EC-46E1-84DB-96F0DDA67AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{461370FB-6990-4493-97C3-DDE058616D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{D48BDCD1-ADE3-4EE7-A9DB-3C7F51FF7246}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="455">
   <si>
     <t>Stage 1</t>
   </si>
@@ -1401,6 +1401,9 @@
   </si>
   <si>
     <t>Tour de France</t>
+  </si>
+  <si>
+    <t>Torstein Træen</t>
   </si>
 </sst>
 </file>
@@ -1779,7 +1782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6820EB03-3F7F-49BA-9E92-28FA32BF7E1D}">
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -6707,6 +6710,47 @@
       </c>
       <c r="M120" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B121" t="s">
+        <v>453</v>
+      </c>
+      <c r="C121" t="s">
+        <v>51</v>
+      </c>
+      <c r="D121" t="s">
+        <v>256</v>
+      </c>
+      <c r="E121" t="s">
+        <v>291</v>
+      </c>
+      <c r="F121" t="s">
+        <v>93</v>
+      </c>
+      <c r="G121" t="s">
+        <v>329</v>
+      </c>
+      <c r="H121" t="s">
+        <v>322</v>
+      </c>
+      <c r="I121" t="s">
+        <v>149</v>
+      </c>
+      <c r="J121" t="s">
+        <v>338</v>
+      </c>
+      <c r="K121" t="s">
+        <v>454</v>
+      </c>
+      <c r="L121" t="s">
+        <v>362</v>
+      </c>
+      <c r="M121" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8395,6 +8395,71 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tour de France</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Stage 6</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Tadej Pogačar</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Paul Seixas</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Juan Ayuso</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Florian Lipowitz</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Mattias Skjelmose</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Lenny Martinez</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Sepp Kuss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20">
     <sortState ref="A2:M69">

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8241,12 +8241,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
+          <t>Florian Lipowitz</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
           <t>Lennert Van Eetvelt</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Florian Lipowitz</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8306,14 +8306,14 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
+          <t>Sean Quinn</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
           <t>Kévin Vauquelin</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Sean Quinn</t>
-        </is>
-      </c>
       <c r="K121" t="inlineStr">
         <is>
           <t>Torstein Traeen</t>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
+          <t>Pablo Castrillo</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
           <t>Mathias Vacek</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>Pablo Castrillo</t>
         </is>
       </c>
     </row>
@@ -8371,14 +8371,14 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
           <t>Biniam Girmay</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Mads Pedersen</t>
-        </is>
-      </c>
       <c r="K122" t="inlineStr">
         <is>
           <t>Milan Fretin</t>
@@ -8386,12 +8386,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
+          <t>Anthony Turgis</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
           <t>Soren Waerenskjold</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>Anthony Turgis</t>
         </is>
       </c>
     </row>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
+          <t>Florian Lipowitz</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
           <t>Lennert Van Eetvelt</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Florian Lipowitz</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8306,14 +8306,14 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
+          <t>Sean Quinn</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
           <t>Kévin Vauquelin</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Sean Quinn</t>
-        </is>
-      </c>
       <c r="K121" t="inlineStr">
         <is>
           <t>Torstein Traeen</t>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
+          <t>Pablo Castrillo</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
           <t>Mathias Vacek</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>Pablo Castrillo</t>
         </is>
       </c>
     </row>
@@ -8371,14 +8371,14 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
           <t>Biniam Girmay</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Mads Pedersen</t>
-        </is>
-      </c>
       <c r="K122" t="inlineStr">
         <is>
           <t>Milan Fretin</t>
@@ -8386,12 +8386,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
+          <t>Anthony Turgis</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
           <t>Soren Waerenskjold</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>Anthony Turgis</t>
         </is>
       </c>
     </row>
@@ -8457,6 +8457,71 @@
       <c r="M123" t="inlineStr">
         <is>
           <t>Sepp Kuss</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Tour de France</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Stage 7</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Tim Merlier</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Soren Waerenskjold</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Biniam Girmay</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Max Kanter</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Jasper Philipsen</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Phil Bauhaus</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Huub Artz</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Dorian Godon</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Tom Van Asbroeck</t>
         </is>
       </c>
     </row>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8180,12 +8180,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
+          <t>Lenny Martinez</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
           <t>Paul Seixas</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>Lenny Martinez</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
+          <t>Lennert Van Eetvelt</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
           <t>Florian Lipowitz</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Lennert Van Eetvelt</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
+          <t>Kévin Vauquelin</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
           <t>Sean Quinn</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Kévin Vauquelin</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8495,22 +8495,22 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
+          <t>Huub Artz</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
           <t>Phil Bauhaus</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>Huub Artz</t>
-        </is>
-      </c>
       <c r="K124" t="inlineStr">
         <is>
+          <t>Dorian Godon</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
           <t>Mads Pedersen</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Dorian Godon</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8180,12 +8180,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
+          <t>Paul Seixas</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
           <t>Lenny Martinez</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>Paul Seixas</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
+          <t>Florian Lipowitz</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
           <t>Lennert Van Eetvelt</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Florian Lipowitz</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
+          <t>Sean Quinn</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
           <t>Kévin Vauquelin</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Sean Quinn</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8495,22 +8495,22 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
+          <t>Phil Bauhaus</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
           <t>Huub Artz</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>Phil Bauhaus</t>
-        </is>
-      </c>
       <c r="K124" t="inlineStr">
         <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
           <t>Dorian Godon</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Mads Pedersen</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -8581,6 +8581,71 @@
       <c r="M125" t="inlineStr">
         <is>
           <t>Milan Fretin</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Tour de France</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Stage 9</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Mathieu Van Der Poel</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Tobias Halland Johannessen</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tom Pidcock</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Alex Baudin</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Filippo Ganna</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Michael Matthews</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Jordan Jegat</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Nicolas Breuillard</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Sean Quinn</t>
         </is>
       </c>
     </row>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{0957F064-53D0-4088-BBF0-4B1F6E79A909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDD7203D-273D-4AAE-AE2A-6B4A95D10529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="457">
   <si>
     <t>Date</t>
   </si>
@@ -1413,10 +1413,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1779,17 +1785,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M126"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M127"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1830,7 +1836,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -1871,7 +1877,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1912,7 +1918,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1953,7 +1959,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1994,7 +2000,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2035,7 +2041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2076,7 +2082,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2117,7 +2123,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2158,7 +2164,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2199,7 +2205,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2240,7 +2246,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2281,7 +2287,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2322,7 +2328,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2363,7 +2369,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2404,7 +2410,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2445,7 +2451,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2486,7 +2492,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -2527,7 +2533,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -2568,7 +2574,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -2609,7 +2615,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2650,7 +2656,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2691,7 +2697,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2732,7 +2738,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2773,7 +2779,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -2814,7 +2820,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -2855,7 +2861,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -2896,7 +2902,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -2937,7 +2943,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -2978,7 +2984,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3019,7 +3025,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3060,7 +3066,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3101,7 +3107,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3142,7 +3148,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3183,7 +3189,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3224,7 +3230,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3265,7 +3271,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3306,7 +3312,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3347,7 +3353,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3388,7 +3394,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3429,7 +3435,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -3470,7 +3476,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -3511,7 +3517,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -3552,7 +3558,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -3593,7 +3599,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -3634,7 +3640,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -3675,7 +3681,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -3716,7 +3722,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -3757,7 +3763,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -3798,7 +3804,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -3839,7 +3845,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -3880,7 +3886,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -3921,7 +3927,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -3962,7 +3968,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4003,7 +4009,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4044,7 +4050,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4085,7 +4091,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4126,7 +4132,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4167,7 +4173,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4208,7 +4214,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4249,7 +4255,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4290,7 +4296,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4331,7 +4337,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4372,7 +4378,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4413,7 +4419,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4454,7 +4460,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -4495,7 +4501,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -4536,7 +4542,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -4577,7 +4583,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -4618,7 +4624,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -4659,7 +4665,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -4700,7 +4706,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -4741,7 +4747,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -4782,7 +4788,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -4823,7 +4829,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -4864,7 +4870,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -4905,7 +4911,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -4946,7 +4952,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -4987,7 +4993,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5028,7 +5034,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5069,7 +5075,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5110,7 +5116,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5151,7 +5157,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5192,7 +5198,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5233,7 +5239,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5274,7 +5280,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5315,7 +5321,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5356,7 +5362,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5397,7 +5403,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5438,7 +5444,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -5479,7 +5485,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -5520,7 +5526,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -5561,7 +5567,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -5602,7 +5608,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -5643,7 +5649,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -5684,7 +5690,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -5725,7 +5731,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -5766,7 +5772,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -5807,7 +5813,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -5848,7 +5854,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -5889,7 +5895,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -5930,7 +5936,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -5971,7 +5977,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6012,7 +6018,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6053,7 +6059,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6094,7 +6100,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6135,7 +6141,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6176,7 +6182,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6217,7 +6223,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6258,7 +6264,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6299,7 +6305,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6340,7 +6346,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6381,7 +6387,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6422,7 +6428,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6463,7 +6469,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -6504,7 +6510,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -6545,7 +6551,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -6586,7 +6592,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -6627,7 +6633,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -6668,7 +6674,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -6709,7 +6715,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -6750,7 +6756,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -6791,7 +6797,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -6832,7 +6838,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -6873,7 +6879,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -6914,7 +6920,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -6953,6 +6959,47 @@
       </c>
       <c r="M126" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B127" t="s">
+        <v>448</v>
+      </c>
+      <c r="C127" t="s">
+        <v>378</v>
+      </c>
+      <c r="D127" t="s">
+        <v>202</v>
+      </c>
+      <c r="E127" t="s">
+        <v>74</v>
+      </c>
+      <c r="F127" t="s">
+        <v>137</v>
+      </c>
+      <c r="G127" t="s">
+        <v>157</v>
+      </c>
+      <c r="H127" t="s">
+        <v>138</v>
+      </c>
+      <c r="I127" t="s">
+        <v>181</v>
+      </c>
+      <c r="J127" t="s">
+        <v>221</v>
+      </c>
+      <c r="K127" t="s">
+        <v>428</v>
+      </c>
+      <c r="L127" t="s">
+        <v>204</v>
+      </c>
+      <c r="M127" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -6961,6 +7008,7 @@
       <sortCondition ref="A1:A20"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDD7203D-273D-4AAE-AE2A-6B4A95D10529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F50F7B3-1BA9-45A2-A8E7-1EDDE00CAD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="459">
   <si>
     <t>Date</t>
   </si>
@@ -1407,6 +1407,12 @@
   </si>
   <si>
     <t>Nicolas Breuillard</t>
+  </si>
+  <si>
+    <t>Clément Russo</t>
+  </si>
+  <si>
+    <t>Fernando Gaviria</t>
   </si>
 </sst>
 </file>
@@ -1785,7 +1791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -7000,6 +7006,47 @@
       </c>
       <c r="M127" t="s">
         <v>179</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B128" t="s">
+        <v>448</v>
+      </c>
+      <c r="C128" t="s">
+        <v>383</v>
+      </c>
+      <c r="D128" t="s">
+        <v>452</v>
+      </c>
+      <c r="E128" t="s">
+        <v>450</v>
+      </c>
+      <c r="F128" t="s">
+        <v>124</v>
+      </c>
+      <c r="G128" t="s">
+        <v>209</v>
+      </c>
+      <c r="H128" t="s">
+        <v>451</v>
+      </c>
+      <c r="I128" t="s">
+        <v>64</v>
+      </c>
+      <c r="J128" t="s">
+        <v>175</v>
+      </c>
+      <c r="K128" t="s">
+        <v>457</v>
+      </c>
+      <c r="L128" t="s">
+        <v>458</v>
+      </c>
+      <c r="M128" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F50F7B3-1BA9-45A2-A8E7-1EDDE00CAD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{8F50F7B3-1BA9-45A2-A8E7-1EDDE00CAD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EDFA170-6411-4648-AF31-133F4221F5B6}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7025,28 +7025,28 @@
         <v>450</v>
       </c>
       <c r="F128" t="s">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="G128" t="s">
-        <v>209</v>
+        <v>451</v>
       </c>
       <c r="H128" t="s">
-        <v>451</v>
+        <v>64</v>
       </c>
       <c r="I128" t="s">
-        <v>64</v>
+        <v>175</v>
       </c>
       <c r="J128" t="s">
-        <v>175</v>
+        <v>457</v>
       </c>
       <c r="K128" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L128" t="s">
-        <v>458</v>
+        <v>126</v>
       </c>
       <c r="M128" t="s">
-        <v>126</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{8F50F7B3-1BA9-45A2-A8E7-1EDDE00CAD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EDFA170-6411-4648-AF31-133F4221F5B6}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{8F50F7B3-1BA9-45A2-A8E7-1EDDE00CAD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6503C281-08E7-4230-A90E-7F7DCF109061}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7025,28 +7025,28 @@
         <v>450</v>
       </c>
       <c r="F128" t="s">
+        <v>124</v>
+      </c>
+      <c r="G128" t="s">
         <v>209</v>
       </c>
-      <c r="G128" t="s">
+      <c r="H128" t="s">
         <v>451</v>
       </c>
-      <c r="H128" t="s">
+      <c r="I128" t="s">
         <v>64</v>
       </c>
-      <c r="I128" t="s">
+      <c r="J128" t="s">
         <v>175</v>
       </c>
-      <c r="J128" t="s">
+      <c r="K128" t="s">
         <v>457</v>
       </c>
-      <c r="K128" t="s">
+      <c r="L128" t="s">
         <v>458</v>
       </c>
-      <c r="L128" t="s">
+      <c r="M128" t="s">
         <v>126</v>
-      </c>
-      <c r="M128" t="s">
-        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8594,7 +8594,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" t="n">
         <v>46215</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129" s="2" t="n">
         <v>46219</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -8850,6 +8850,71 @@
       <c r="M129" t="inlineStr">
         <is>
           <t>Huub Artz</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Tour de France</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Stage 13</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Mauro Schmid</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Harold Tejada</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Tom Pidcock</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Maxim Van Gils</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Brandon Mcnulty</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Jordan Jegat</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Kévin Vauquelin</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Clement Braz Afonso</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Tim Wellens</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Luke Plapp</t>
         </is>
       </c>
     </row>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8918,6 +8918,71 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Tour de France</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Stage 14</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Tadej Pogačar</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Paul Seixas</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Florian Lipowitz</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Juan Ayuso</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Richard Carapaz</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Tobias Halland Johannessen</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Mattias Skjelmose</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20">
     <sortState ref="A2:M69">

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB682E32-797E-4F8B-8DD7-BEA530AE4C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D75B900D-A77A-4BB4-93E5-ACF257581C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="462">
   <si>
     <t>Date</t>
   </si>
@@ -1409,25 +1409,19 @@
   </si>
   <si>
     <t>Bruno Armirail</t>
-  </si>
-  <si>
-    <t>Clément Russo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1453,9 +1447,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1790,7 +1785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -6639,7 +6634,7 @@
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
+      <c r="A119">
         <v>46208</v>
       </c>
       <c r="B119" t="s">
@@ -6680,7 +6675,7 @@
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
+      <c r="A120">
         <v>46209</v>
       </c>
       <c r="B120" t="s">
@@ -6721,7 +6716,7 @@
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
+      <c r="A121">
         <v>46210</v>
       </c>
       <c r="B121" t="s">
@@ -6762,7 +6757,7 @@
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
+      <c r="A122">
         <v>46211</v>
       </c>
       <c r="B122" t="s">
@@ -6803,7 +6798,7 @@
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
+      <c r="A123">
         <v>46212</v>
       </c>
       <c r="B123" t="s">
@@ -6844,7 +6839,7 @@
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
+      <c r="A124">
         <v>46213</v>
       </c>
       <c r="B124" t="s">
@@ -6885,7 +6880,7 @@
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
+      <c r="A125">
         <v>46214</v>
       </c>
       <c r="B125" t="s">
@@ -6926,7 +6921,7 @@
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
+      <c r="A126">
         <v>46215</v>
       </c>
       <c r="B126" t="s">
@@ -6967,7 +6962,7 @@
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
+      <c r="A127" s="2">
         <v>46217</v>
       </c>
       <c r="B127" t="s">
@@ -7008,7 +7003,7 @@
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
+      <c r="A128" s="2">
         <v>46218</v>
       </c>
       <c r="B128" t="s">
@@ -7049,7 +7044,7 @@
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
+      <c r="A129" s="2">
         <v>46219</v>
       </c>
       <c r="B129" t="s">
@@ -7090,7 +7085,7 @@
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A130" s="1">
+      <c r="A130">
         <v>46220</v>
       </c>
       <c r="B130" t="s">
@@ -7131,7 +7126,7 @@
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
+      <c r="A131">
         <v>46221</v>
       </c>
       <c r="B131" t="s">
@@ -7172,7 +7167,7 @@
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="1">
+      <c r="A132">
         <v>46222</v>
       </c>
       <c r="B132" t="s">
@@ -7213,7 +7208,7 @@
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="1">
+      <c r="A133">
         <v>46224</v>
       </c>
       <c r="B133" t="s">
@@ -7254,7 +7249,7 @@
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="1">
+      <c r="A134">
         <v>46225</v>
       </c>
       <c r="B134" t="s">
@@ -7279,7 +7274,7 @@
         <v>454</v>
       </c>
       <c r="I134" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="J134" t="s">
         <v>451</v>
@@ -7292,6 +7287,47 @@
       </c>
       <c r="M134" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>46226</v>
+      </c>
+      <c r="B135" t="s">
+        <v>448</v>
+      </c>
+      <c r="C135" t="s">
+        <v>404</v>
+      </c>
+      <c r="D135" t="s">
+        <v>280</v>
+      </c>
+      <c r="E135" t="s">
+        <v>20</v>
+      </c>
+      <c r="F135" t="s">
+        <v>180</v>
+      </c>
+      <c r="G135" t="s">
+        <v>227</v>
+      </c>
+      <c r="H135" t="s">
+        <v>107</v>
+      </c>
+      <c r="I135" t="s">
+        <v>358</v>
+      </c>
+      <c r="J135" t="s">
+        <v>93</v>
+      </c>
+      <c r="K135" t="s">
+        <v>179</v>
+      </c>
+      <c r="L135" t="s">
+        <v>74</v>
+      </c>
+      <c r="M135" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -7300,7 +7336,6 @@
       <sortCondition ref="A1:A20"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9304,6 +9304,71 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Tour de France</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Stage 20</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Richard Carapaz</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Sepp Kuss</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Tadej Pogačar</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Jai Hindley</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Lenny Martinez</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Mattias Skjelmose</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Juan Ayuso</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Paul Seixas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20">
     <sortState ref="A2:M69">

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9369,6 +9369,71 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Tour de France</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Stage 21</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Mathieu Van Der Poel</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Jasper Philipsen</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Max Kanter</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Olav Kooij</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Matej Mohoric</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Rick Pluimers</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Anthony Turgis</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Clement Russo</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Milan Fretin</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20">
     <sortState ref="A2:M69">

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE7D74FD-97D9-48DD-A2A6-051F6F1B0DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{FE7D74FD-97D9-48DD-A2A6-051F6F1B0DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{271267CD-AFE0-48A0-B1A4-400D1B4317E1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="460">
   <si>
     <t>Date</t>
   </si>
@@ -1343,9 +1343,6 @@
   </si>
   <si>
     <t>Marijn Van Den Berg</t>
-  </si>
-  <si>
-    <t>Mathieu Van Der Poel</t>
   </si>
   <si>
     <t>Michael Matthews</t>
@@ -4105,7 +4102,7 @@
         <v>205</v>
       </c>
       <c r="F57" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G57" t="s">
         <v>64</v>
@@ -6530,7 +6527,7 @@
         <v>439</v>
       </c>
       <c r="H116" t="s">
-        <v>440</v>
+        <v>171</v>
       </c>
       <c r="I116" t="s">
         <v>256</v>
@@ -6539,10 +6536,10 @@
         <v>296</v>
       </c>
       <c r="K116" t="s">
+        <v>440</v>
+      </c>
+      <c r="L116" t="s">
         <v>441</v>
-      </c>
-      <c r="L116" t="s">
-        <v>442</v>
       </c>
       <c r="M116" t="s">
         <v>48</v>
@@ -6562,22 +6559,22 @@
         <v>202</v>
       </c>
       <c r="E117" t="s">
-        <v>440</v>
+        <v>171</v>
       </c>
       <c r="F117" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G117" t="s">
         <v>75</v>
       </c>
       <c r="H117" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I117" t="s">
         <v>80</v>
       </c>
       <c r="J117" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K117" t="s">
         <v>20</v>
@@ -6621,7 +6618,7 @@
         <v>280</v>
       </c>
       <c r="K118" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L118" t="s">
         <v>104</v>
@@ -6635,7 +6632,7 @@
         <v>46208</v>
       </c>
       <c r="B119" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C119" t="s">
         <v>34</v>
@@ -6676,7 +6673,7 @@
         <v>46209</v>
       </c>
       <c r="B120" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C120" t="s">
         <v>43</v>
@@ -6717,7 +6714,7 @@
         <v>46210</v>
       </c>
       <c r="B121" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C121" t="s">
         <v>51</v>
@@ -6744,7 +6741,7 @@
         <v>144</v>
       </c>
       <c r="K121" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L121" t="s">
         <v>357</v>
@@ -6758,13 +6755,13 @@
         <v>46211</v>
       </c>
       <c r="B122" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C122" t="s">
         <v>55</v>
       </c>
       <c r="D122" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E122" t="s">
         <v>269</v>
@@ -6773,7 +6770,7 @@
         <v>302</v>
       </c>
       <c r="G122" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H122" t="s">
         <v>124</v>
@@ -6791,7 +6788,7 @@
         <v>175</v>
       </c>
       <c r="M122" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
@@ -6799,7 +6796,7 @@
         <v>46212</v>
       </c>
       <c r="B123" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C123" t="s">
         <v>158</v>
@@ -6840,7 +6837,7 @@
         <v>46213</v>
       </c>
       <c r="B124" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C124" t="s">
         <v>166</v>
@@ -6849,7 +6846,7 @@
         <v>302</v>
       </c>
       <c r="E124" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F124" t="s">
         <v>64</v>
@@ -6864,7 +6861,7 @@
         <v>424</v>
       </c>
       <c r="J124" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K124" t="s">
         <v>255</v>
@@ -6873,7 +6870,7 @@
         <v>191</v>
       </c>
       <c r="M124" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -6881,7 +6878,7 @@
         <v>46214</v>
       </c>
       <c r="B125" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C125" t="s">
         <v>236</v>
@@ -6893,7 +6890,7 @@
         <v>64</v>
       </c>
       <c r="F125" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G125" t="s">
         <v>124</v>
@@ -6902,7 +6899,7 @@
         <v>123</v>
       </c>
       <c r="I125" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J125" t="s">
         <v>126</v>
@@ -6911,7 +6908,7 @@
         <v>269</v>
       </c>
       <c r="L125" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M125" t="s">
         <v>209</v>
@@ -6922,13 +6919,13 @@
         <v>46215</v>
       </c>
       <c r="B126" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C126" t="s">
         <v>375</v>
       </c>
       <c r="D126" t="s">
-        <v>440</v>
+        <v>171</v>
       </c>
       <c r="E126" t="s">
         <v>107</v>
@@ -6946,13 +6943,13 @@
         <v>255</v>
       </c>
       <c r="J126" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K126" t="s">
         <v>418</v>
       </c>
       <c r="L126" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="M126" t="s">
         <v>335</v>
@@ -6963,7 +6960,7 @@
         <v>46217</v>
       </c>
       <c r="B127" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C127" t="s">
         <v>377</v>
@@ -7004,16 +7001,16 @@
         <v>46218</v>
       </c>
       <c r="B128" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C128" t="s">
         <v>382</v>
       </c>
       <c r="D128" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E128" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F128" t="s">
         <v>124</v>
@@ -7022,7 +7019,7 @@
         <v>209</v>
       </c>
       <c r="H128" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I128" t="s">
         <v>64</v>
@@ -7031,10 +7028,10 @@
         <v>175</v>
       </c>
       <c r="K128" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L128" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M128" t="s">
         <v>126</v>
@@ -7045,7 +7042,7 @@
         <v>46219</v>
       </c>
       <c r="B129" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C129" t="s">
         <v>385</v>
@@ -7054,7 +7051,7 @@
         <v>302</v>
       </c>
       <c r="E129" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F129" t="s">
         <v>124</v>
@@ -7072,13 +7069,13 @@
         <v>269</v>
       </c>
       <c r="K129" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L129" t="s">
         <v>255</v>
       </c>
       <c r="M129" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
@@ -7086,7 +7083,7 @@
         <v>46220</v>
       </c>
       <c r="B130" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C130" t="s">
         <v>386</v>
@@ -7104,7 +7101,7 @@
         <v>420</v>
       </c>
       <c r="H130" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I130" t="s">
         <v>418</v>
@@ -7113,10 +7110,10 @@
         <v>144</v>
       </c>
       <c r="K130" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L130" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M130" t="s">
         <v>112</v>
@@ -7127,7 +7124,7 @@
         <v>46221</v>
       </c>
       <c r="B131" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C131" t="s">
         <v>392</v>
@@ -7168,7 +7165,7 @@
         <v>46222</v>
       </c>
       <c r="B132" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C132" t="s">
         <v>394</v>
@@ -7209,7 +7206,7 @@
         <v>46224</v>
       </c>
       <c r="B133" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C133" t="s">
         <v>398</v>
@@ -7233,10 +7230,10 @@
         <v>154</v>
       </c>
       <c r="J133" t="s">
+        <v>457</v>
+      </c>
+      <c r="K133" t="s">
         <v>458</v>
-      </c>
-      <c r="K133" t="s">
-        <v>459</v>
       </c>
       <c r="L133" t="s">
         <v>357</v>
@@ -7250,7 +7247,7 @@
         <v>46225</v>
       </c>
       <c r="B134" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C134" t="s">
         <v>399</v>
@@ -7262,25 +7259,25 @@
         <v>20</v>
       </c>
       <c r="F134" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G134" t="s">
         <v>232</v>
       </c>
       <c r="H134" t="s">
+        <v>451</v>
+      </c>
+      <c r="I134" t="s">
         <v>452</v>
       </c>
-      <c r="I134" t="s">
-        <v>453</v>
-      </c>
       <c r="J134" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K134" t="s">
         <v>255</v>
       </c>
       <c r="L134" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M134" t="s">
         <v>46</v>
@@ -7291,7 +7288,7 @@
         <v>46226</v>
       </c>
       <c r="B135" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C135" t="s">
         <v>403</v>
@@ -7332,7 +7329,7 @@
         <v>46227</v>
       </c>
       <c r="B136" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C136" t="s">
         <v>404</v>
@@ -7373,7 +7370,7 @@
         <v>46228</v>
       </c>
       <c r="B137" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C137" t="s">
         <v>405</v>
@@ -7414,13 +7411,13 @@
         <v>46229</v>
       </c>
       <c r="B138" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C138" t="s">
         <v>406</v>
       </c>
       <c r="D138" t="s">
-        <v>440</v>
+        <v>171</v>
       </c>
       <c r="E138" t="s">
         <v>124</v>
@@ -7432,19 +7429,19 @@
         <v>269</v>
       </c>
       <c r="H138" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I138" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J138" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K138" t="s">
         <v>175</v>
       </c>
       <c r="L138" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M138" t="s">
         <v>209</v>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{FE7D74FD-97D9-48DD-A2A6-051F6F1B0DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{271267CD-AFE0-48A0-B1A4-400D1B4317E1}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{FE7D74FD-97D9-48DD-A2A6-051F6F1B0DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49B02058-CA25-4226-9849-9CAB7A585F46}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="459">
   <si>
     <t>Date</t>
   </si>
@@ -1292,9 +1292,6 @@
   </si>
   <si>
     <t>Jan Castellon</t>
-  </si>
-  <si>
-    <t>Wout Van Aert</t>
   </si>
   <si>
     <t>Phil Bauhaus</t>
@@ -4102,7 +4099,7 @@
         <v>205</v>
       </c>
       <c r="F57" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G57" t="s">
         <v>64</v>
@@ -6228,13 +6225,13 @@
         <v>55</v>
       </c>
       <c r="D109" t="s">
-        <v>423</v>
+        <v>205</v>
       </c>
       <c r="E109" t="s">
         <v>161</v>
       </c>
       <c r="F109" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G109" t="s">
         <v>207</v>
@@ -6278,7 +6275,7 @@
         <v>358</v>
       </c>
       <c r="G110" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H110" t="s">
         <v>93</v>
@@ -6290,7 +6287,7 @@
         <v>418</v>
       </c>
       <c r="K110" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L110" t="s">
         <v>298</v>
@@ -6331,10 +6328,10 @@
         <v>137</v>
       </c>
       <c r="K111" t="s">
+        <v>425</v>
+      </c>
+      <c r="L111" t="s">
         <v>426</v>
-      </c>
-      <c r="L111" t="s">
-        <v>427</v>
       </c>
       <c r="M111" t="s">
         <v>422</v>
@@ -6363,10 +6360,10 @@
         <v>181</v>
       </c>
       <c r="H112" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I112" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J112" t="s">
         <v>420</v>
@@ -6386,7 +6383,7 @@
         <v>46187</v>
       </c>
       <c r="B113" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C113" t="s">
         <v>60</v>
@@ -6404,7 +6401,7 @@
         <v>360</v>
       </c>
       <c r="H113" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I113" t="s">
         <v>214</v>
@@ -6413,13 +6410,13 @@
         <v>408</v>
       </c>
       <c r="K113" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L113" t="s">
         <v>115</v>
       </c>
       <c r="M113" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -6427,7 +6424,7 @@
         <v>46190</v>
       </c>
       <c r="B114" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C114" t="s">
         <v>25</v>
@@ -6451,7 +6448,7 @@
         <v>79</v>
       </c>
       <c r="J114" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K114" t="s">
         <v>80</v>
@@ -6468,7 +6465,7 @@
         <v>46191</v>
       </c>
       <c r="B115" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C115" t="s">
         <v>34</v>
@@ -6477,16 +6474,16 @@
         <v>188</v>
       </c>
       <c r="E115" t="s">
+        <v>434</v>
+      </c>
+      <c r="F115" t="s">
         <v>435</v>
-      </c>
-      <c r="F115" t="s">
-        <v>436</v>
       </c>
       <c r="G115" t="s">
         <v>37</v>
       </c>
       <c r="H115" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I115" t="s">
         <v>75</v>
@@ -6509,7 +6506,7 @@
         <v>46192</v>
       </c>
       <c r="B116" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C116" t="s">
         <v>43</v>
@@ -6518,13 +6515,13 @@
         <v>35</v>
       </c>
       <c r="E116" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F116" t="s">
         <v>86</v>
       </c>
       <c r="G116" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H116" t="s">
         <v>171</v>
@@ -6536,10 +6533,10 @@
         <v>296</v>
       </c>
       <c r="K116" t="s">
+        <v>439</v>
+      </c>
+      <c r="L116" t="s">
         <v>440</v>
-      </c>
-      <c r="L116" t="s">
-        <v>441</v>
       </c>
       <c r="M116" t="s">
         <v>48</v>
@@ -6550,7 +6547,7 @@
         <v>46193</v>
       </c>
       <c r="B117" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C117" t="s">
         <v>51</v>
@@ -6562,19 +6559,19 @@
         <v>171</v>
       </c>
       <c r="F117" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G117" t="s">
         <v>75</v>
       </c>
       <c r="H117" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I117" t="s">
         <v>80</v>
       </c>
       <c r="J117" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K117" t="s">
         <v>20</v>
@@ -6591,7 +6588,7 @@
         <v>46194</v>
       </c>
       <c r="B118" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C118" t="s">
         <v>55</v>
@@ -6603,7 +6600,7 @@
         <v>179</v>
       </c>
       <c r="F118" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G118" t="s">
         <v>167</v>
@@ -6618,7 +6615,7 @@
         <v>280</v>
       </c>
       <c r="K118" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L118" t="s">
         <v>104</v>
@@ -6632,7 +6629,7 @@
         <v>46208</v>
       </c>
       <c r="B119" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C119" t="s">
         <v>34</v>
@@ -6673,7 +6670,7 @@
         <v>46209</v>
       </c>
       <c r="B120" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C120" t="s">
         <v>43</v>
@@ -6714,7 +6711,7 @@
         <v>46210</v>
       </c>
       <c r="B121" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C121" t="s">
         <v>51</v>
@@ -6741,7 +6738,7 @@
         <v>144</v>
       </c>
       <c r="K121" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L121" t="s">
         <v>357</v>
@@ -6755,13 +6752,13 @@
         <v>46211</v>
       </c>
       <c r="B122" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C122" t="s">
         <v>55</v>
       </c>
       <c r="D122" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E122" t="s">
         <v>269</v>
@@ -6770,7 +6767,7 @@
         <v>302</v>
       </c>
       <c r="G122" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H122" t="s">
         <v>124</v>
@@ -6788,7 +6785,7 @@
         <v>175</v>
       </c>
       <c r="M122" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
@@ -6796,7 +6793,7 @@
         <v>46212</v>
       </c>
       <c r="B123" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C123" t="s">
         <v>158</v>
@@ -6837,7 +6834,7 @@
         <v>46213</v>
       </c>
       <c r="B124" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C124" t="s">
         <v>166</v>
@@ -6846,7 +6843,7 @@
         <v>302</v>
       </c>
       <c r="E124" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F124" t="s">
         <v>64</v>
@@ -6858,10 +6855,10 @@
         <v>124</v>
       </c>
       <c r="I124" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J124" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K124" t="s">
         <v>255</v>
@@ -6870,7 +6867,7 @@
         <v>191</v>
       </c>
       <c r="M124" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -6878,7 +6875,7 @@
         <v>46214</v>
       </c>
       <c r="B125" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C125" t="s">
         <v>236</v>
@@ -6890,7 +6887,7 @@
         <v>64</v>
       </c>
       <c r="F125" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G125" t="s">
         <v>124</v>
@@ -6899,7 +6896,7 @@
         <v>123</v>
       </c>
       <c r="I125" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="J125" t="s">
         <v>126</v>
@@ -6908,7 +6905,7 @@
         <v>269</v>
       </c>
       <c r="L125" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M125" t="s">
         <v>209</v>
@@ -6919,7 +6916,7 @@
         <v>46215</v>
       </c>
       <c r="B126" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C126" t="s">
         <v>375</v>
@@ -6943,13 +6940,13 @@
         <v>255</v>
       </c>
       <c r="J126" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K126" t="s">
         <v>418</v>
       </c>
       <c r="L126" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M126" t="s">
         <v>335</v>
@@ -6960,7 +6957,7 @@
         <v>46217</v>
       </c>
       <c r="B127" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C127" t="s">
         <v>377</v>
@@ -7001,16 +6998,16 @@
         <v>46218</v>
       </c>
       <c r="B128" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C128" t="s">
         <v>382</v>
       </c>
       <c r="D128" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E128" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F128" t="s">
         <v>124</v>
@@ -7019,7 +7016,7 @@
         <v>209</v>
       </c>
       <c r="H128" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I128" t="s">
         <v>64</v>
@@ -7028,10 +7025,10 @@
         <v>175</v>
       </c>
       <c r="K128" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L128" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="M128" t="s">
         <v>126</v>
@@ -7042,7 +7039,7 @@
         <v>46219</v>
       </c>
       <c r="B129" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C129" t="s">
         <v>385</v>
@@ -7051,7 +7048,7 @@
         <v>302</v>
       </c>
       <c r="E129" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F129" t="s">
         <v>124</v>
@@ -7069,13 +7066,13 @@
         <v>269</v>
       </c>
       <c r="K129" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L129" t="s">
         <v>255</v>
       </c>
       <c r="M129" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
@@ -7083,7 +7080,7 @@
         <v>46220</v>
       </c>
       <c r="B130" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C130" t="s">
         <v>386</v>
@@ -7101,7 +7098,7 @@
         <v>420</v>
       </c>
       <c r="H130" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I130" t="s">
         <v>418</v>
@@ -7110,10 +7107,10 @@
         <v>144</v>
       </c>
       <c r="K130" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L130" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M130" t="s">
         <v>112</v>
@@ -7124,7 +7121,7 @@
         <v>46221</v>
       </c>
       <c r="B131" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C131" t="s">
         <v>392</v>
@@ -7165,7 +7162,7 @@
         <v>46222</v>
       </c>
       <c r="B132" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C132" t="s">
         <v>394</v>
@@ -7206,7 +7203,7 @@
         <v>46224</v>
       </c>
       <c r="B133" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C133" t="s">
         <v>398</v>
@@ -7230,10 +7227,10 @@
         <v>154</v>
       </c>
       <c r="J133" t="s">
+        <v>456</v>
+      </c>
+      <c r="K133" t="s">
         <v>457</v>
-      </c>
-      <c r="K133" t="s">
-        <v>458</v>
       </c>
       <c r="L133" t="s">
         <v>357</v>
@@ -7247,7 +7244,7 @@
         <v>46225</v>
       </c>
       <c r="B134" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C134" t="s">
         <v>399</v>
@@ -7259,25 +7256,25 @@
         <v>20</v>
       </c>
       <c r="F134" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G134" t="s">
         <v>232</v>
       </c>
       <c r="H134" t="s">
+        <v>450</v>
+      </c>
+      <c r="I134" t="s">
         <v>451</v>
       </c>
-      <c r="I134" t="s">
-        <v>452</v>
-      </c>
       <c r="J134" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K134" t="s">
         <v>255</v>
       </c>
       <c r="L134" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M134" t="s">
         <v>46</v>
@@ -7288,7 +7285,7 @@
         <v>46226</v>
       </c>
       <c r="B135" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C135" t="s">
         <v>403</v>
@@ -7329,7 +7326,7 @@
         <v>46227</v>
       </c>
       <c r="B136" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C136" t="s">
         <v>404</v>
@@ -7370,7 +7367,7 @@
         <v>46228</v>
       </c>
       <c r="B137" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C137" t="s">
         <v>405</v>
@@ -7411,7 +7408,7 @@
         <v>46229</v>
       </c>
       <c r="B138" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C138" t="s">
         <v>406</v>
@@ -7429,19 +7426,19 @@
         <v>269</v>
       </c>
       <c r="H138" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I138" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J138" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K138" t="s">
         <v>175</v>
       </c>
       <c r="L138" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M138" t="s">
         <v>209</v>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{FE7D74FD-97D9-48DD-A2A6-051F6F1B0DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49B02058-CA25-4226-9849-9CAB7A585F46}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{804C6C43-F9E8-462B-A9CE-75428B96E99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="461">
   <si>
     <t>Date</t>
   </si>
@@ -1400,6 +1400,12 @@
   </si>
   <si>
     <t>Matej Mohoric</t>
+  </si>
+  <si>
+    <t>Donostia San Sebastian Klasikoa</t>
+  </si>
+  <si>
+    <t>Marc Hirschi</t>
   </si>
 </sst>
 </file>
@@ -1409,7 +1415,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1417,16 +1423,316 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1434,17 +1740,207 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1776,17 +2272,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M138"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M139"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1827,7 +2323,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -1868,7 +2364,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -1909,7 +2405,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -1950,7 +2446,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -1991,7 +2487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2032,7 +2528,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2073,7 +2569,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2114,7 +2610,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2155,7 +2651,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2196,7 +2692,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2237,7 +2733,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2278,7 +2774,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2319,7 +2815,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2360,7 +2856,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2401,7 +2897,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2442,7 +2938,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2483,7 +2979,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -2524,7 +3020,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -2565,7 +3061,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -2606,7 +3102,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2647,7 +3143,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2688,7 +3184,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2729,7 +3225,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2770,7 +3266,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -2811,7 +3307,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -2852,7 +3348,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -2893,7 +3389,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -2934,7 +3430,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -2975,7 +3471,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3016,7 +3512,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3057,7 +3553,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3098,7 +3594,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3139,7 +3635,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3180,7 +3676,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3221,7 +3717,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3262,7 +3758,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3303,7 +3799,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3344,7 +3840,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3385,7 +3881,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3426,7 +3922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -3467,7 +3963,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -3508,7 +4004,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -3549,7 +4045,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -3590,7 +4086,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -3631,7 +4127,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -3672,7 +4168,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -3713,7 +4209,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -3754,7 +4250,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -3795,7 +4291,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -3836,7 +4332,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -3877,7 +4373,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -3918,7 +4414,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -3959,7 +4455,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4000,7 +4496,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4041,7 +4537,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4082,7 +4578,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4123,7 +4619,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4164,7 +4660,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4205,7 +4701,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4246,7 +4742,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4287,7 +4783,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4328,7 +4824,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4369,7 +4865,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4410,7 +4906,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4451,7 +4947,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -4492,7 +4988,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -4533,7 +5029,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -4574,7 +5070,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -4615,7 +5111,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -4656,7 +5152,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -4697,7 +5193,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -4738,7 +5234,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -4779,7 +5275,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -4820,7 +5316,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -4861,7 +5357,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -4902,7 +5398,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -4943,7 +5439,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -4984,7 +5480,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5025,7 +5521,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5066,7 +5562,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5107,7 +5603,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5148,7 +5644,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5189,7 +5685,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5230,7 +5726,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5271,7 +5767,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5312,7 +5808,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5353,7 +5849,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5394,7 +5890,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5435,7 +5931,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -5476,7 +5972,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -5517,7 +6013,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -5558,7 +6054,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -5599,7 +6095,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -5640,7 +6136,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -5681,7 +6177,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -5722,7 +6218,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -5763,7 +6259,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -5804,7 +6300,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -5845,7 +6341,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -5886,7 +6382,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -5927,7 +6423,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -5968,7 +6464,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6009,7 +6505,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6050,7 +6546,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6091,7 +6587,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6132,7 +6628,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6173,7 +6669,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6214,7 +6710,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6255,7 +6751,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6296,7 +6792,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6337,7 +6833,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6378,7 +6874,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6419,7 +6915,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6460,7 +6956,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -6501,7 +6997,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -6542,7 +7038,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -6583,7 +7079,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -6624,7 +7120,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>46208</v>
       </c>
@@ -6665,7 +7161,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>46209</v>
       </c>
@@ -6706,7 +7202,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>46210</v>
       </c>
@@ -6747,7 +7243,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>46211</v>
       </c>
@@ -6788,7 +7284,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>46212</v>
       </c>
@@ -6829,7 +7325,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>46213</v>
       </c>
@@ -6870,7 +7366,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>46214</v>
       </c>
@@ -6911,7 +7407,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>46215</v>
       </c>
@@ -6952,7 +7448,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>46217</v>
       </c>
@@ -6993,7 +7489,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>46218</v>
       </c>
@@ -7034,7 +7530,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>46219</v>
       </c>
@@ -7075,7 +7571,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>46220</v>
       </c>
@@ -7116,7 +7612,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>46221</v>
       </c>
@@ -7157,7 +7653,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>46222</v>
       </c>
@@ -7198,7 +7694,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>46224</v>
       </c>
@@ -7239,7 +7735,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>46225</v>
       </c>
@@ -7280,7 +7776,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>46226</v>
       </c>
@@ -7321,7 +7817,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>46227</v>
       </c>
@@ -7362,7 +7858,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>46228</v>
       </c>
@@ -7403,7 +7899,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>46229</v>
       </c>
@@ -7442,6 +7938,47 @@
       </c>
       <c r="M138" t="s">
         <v>209</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D139" t="s">
+        <v>74</v>
+      </c>
+      <c r="E139" t="s">
+        <v>280</v>
+      </c>
+      <c r="F139" t="s">
+        <v>295</v>
+      </c>
+      <c r="G139" t="s">
+        <v>192</v>
+      </c>
+      <c r="H139" t="s">
+        <v>306</v>
+      </c>
+      <c r="I139" t="s">
+        <v>218</v>
+      </c>
+      <c r="J139" t="s">
+        <v>178</v>
+      </c>
+      <c r="K139" t="s">
+        <v>460</v>
+      </c>
+      <c r="L139" t="s">
+        <v>434</v>
+      </c>
+      <c r="M139" t="s">
+        <v>412</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{804C6C43-F9E8-462B-A9CE-75428B96E99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A7D673D-89B8-420C-BE54-A23C779DD98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="462">
   <si>
     <t>Date</t>
   </si>
@@ -1406,6 +1406,9 @@
   </si>
   <si>
     <t>Marc Hirschi</t>
+  </si>
+  <si>
+    <t>Tour de Pologne</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1416,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="m/d/yy;@"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1892,11 +1895,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2272,18 +2273,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M139"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M140"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2323,7 +2327,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2364,7 +2368,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2405,7 +2409,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2446,7 +2450,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2487,7 +2491,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2528,7 +2532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2569,7 +2573,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2610,7 +2614,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2651,7 +2655,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2692,7 +2696,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2733,7 +2737,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2774,7 +2778,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2815,7 +2819,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2856,7 +2860,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2897,7 +2901,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2938,7 +2942,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2979,7 +2983,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -3020,7 +3024,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -3061,7 +3065,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -3102,7 +3106,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -3143,7 +3147,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -3184,7 +3188,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -3225,7 +3229,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -3266,7 +3270,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3307,7 +3311,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3348,7 +3352,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3389,7 +3393,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3430,7 +3434,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3471,7 +3475,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3512,7 +3516,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3553,7 +3557,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3594,7 +3598,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3635,7 +3639,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3676,7 +3680,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3717,7 +3721,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3758,7 +3762,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3799,7 +3803,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3840,7 +3844,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3881,7 +3885,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3922,7 +3926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -3963,7 +3967,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -4004,7 +4008,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -4045,7 +4049,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -4086,7 +4090,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -4127,7 +4131,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -4168,7 +4172,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -4209,7 +4213,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -4250,7 +4254,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4291,7 +4295,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4332,7 +4336,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4373,7 +4377,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4414,7 +4418,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4455,7 +4459,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4496,7 +4500,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4537,7 +4541,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4578,7 +4582,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4619,7 +4623,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4660,7 +4664,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4701,7 +4705,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4742,7 +4746,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4783,7 +4787,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4824,7 +4828,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4865,7 +4869,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4906,7 +4910,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4947,7 +4951,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -4988,7 +4992,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -5029,7 +5033,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -5070,7 +5074,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -5111,7 +5115,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -5152,7 +5156,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -5193,7 +5197,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -5234,7 +5238,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -5275,7 +5279,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5316,7 +5320,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5357,7 +5361,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5398,7 +5402,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5439,7 +5443,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5480,7 +5484,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5521,7 +5525,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5562,7 +5566,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5603,7 +5607,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5644,7 +5648,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5685,7 +5689,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5726,7 +5730,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5767,7 +5771,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5808,7 +5812,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5849,7 +5853,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5890,7 +5894,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5931,7 +5935,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -5972,7 +5976,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -6013,7 +6017,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -6054,7 +6058,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -6095,7 +6099,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -6136,7 +6140,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -6177,7 +6181,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -6218,7 +6222,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -6259,7 +6263,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6300,7 +6304,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6341,7 +6345,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6382,7 +6386,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6423,7 +6427,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6464,7 +6468,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6505,7 +6509,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6546,7 +6550,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6587,7 +6591,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6628,7 +6632,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6669,7 +6673,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6710,7 +6714,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6751,7 +6755,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6792,7 +6796,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6833,7 +6837,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6874,7 +6878,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6915,7 +6919,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6956,7 +6960,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -6997,7 +7001,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -7038,7 +7042,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -7079,7 +7083,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -7120,8 +7124,8 @@
         <v>352</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>46208</v>
       </c>
       <c r="B119" t="s">
@@ -7161,8 +7165,8 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
         <v>46209</v>
       </c>
       <c r="B120" t="s">
@@ -7202,8 +7206,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
         <v>46210</v>
       </c>
       <c r="B121" t="s">
@@ -7243,8 +7247,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>46211</v>
       </c>
       <c r="B122" t="s">
@@ -7284,8 +7288,8 @@
         <v>448</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
         <v>46212</v>
       </c>
       <c r="B123" t="s">
@@ -7325,8 +7329,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>46213</v>
       </c>
       <c r="B124" t="s">
@@ -7366,8 +7370,8 @@
         <v>449</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A125">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>46214</v>
       </c>
       <c r="B125" t="s">
@@ -7407,8 +7411,8 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A126">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
         <v>46215</v>
       </c>
       <c r="B126" t="s">
@@ -7448,8 +7452,8 @@
         <v>335</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A127" s="2">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
         <v>46217</v>
       </c>
       <c r="B127" t="s">
@@ -7489,8 +7493,8 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A128" s="2">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
         <v>46218</v>
       </c>
       <c r="B128" t="s">
@@ -7530,8 +7534,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A129" s="2">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
         <v>46219</v>
       </c>
       <c r="B129" t="s">
@@ -7571,8 +7575,8 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A130">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
         <v>46220</v>
       </c>
       <c r="B130" t="s">
@@ -7612,8 +7616,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A131">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
         <v>46221</v>
       </c>
       <c r="B131" t="s">
@@ -7653,8 +7657,8 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A132">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
         <v>46222</v>
       </c>
       <c r="B132" t="s">
@@ -7694,8 +7698,8 @@
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A133">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
         <v>46224</v>
       </c>
       <c r="B133" t="s">
@@ -7735,8 +7739,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A134">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
         <v>46225</v>
       </c>
       <c r="B134" t="s">
@@ -7776,8 +7780,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A135">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
         <v>46226</v>
       </c>
       <c r="B135" t="s">
@@ -7817,8 +7821,8 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A136">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
         <v>46227</v>
       </c>
       <c r="B136" t="s">
@@ -7858,8 +7862,8 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A137">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
         <v>46228</v>
       </c>
       <c r="B137" t="s">
@@ -7899,8 +7903,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A138">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
         <v>46229</v>
       </c>
       <c r="B138" t="s">
@@ -7940,14 +7944,14 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" t="s">
         <v>459</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" t="s">
         <v>60</v>
       </c>
       <c r="D139" t="s">
@@ -7979,6 +7983,47 @@
       </c>
       <c r="M139" t="s">
         <v>412</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B140" t="s">
+        <v>461</v>
+      </c>
+      <c r="C140" t="s">
+        <v>25</v>
+      </c>
+      <c r="D140" t="s">
+        <v>131</v>
+      </c>
+      <c r="E140" t="s">
+        <v>121</v>
+      </c>
+      <c r="F140" t="s">
+        <v>163</v>
+      </c>
+      <c r="G140" t="s">
+        <v>247</v>
+      </c>
+      <c r="H140" t="s">
+        <v>133</v>
+      </c>
+      <c r="I140" t="s">
+        <v>220</v>
+      </c>
+      <c r="J140" t="s">
+        <v>161</v>
+      </c>
+      <c r="K140" t="s">
+        <v>165</v>
+      </c>
+      <c r="L140" t="s">
+        <v>122</v>
+      </c>
+      <c r="M140" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A7D673D-89B8-420C-BE54-A23C779DD98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0D31DF0-EFA6-430A-8721-10706A911FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="464">
   <si>
     <t>Date</t>
   </si>
@@ -1409,6 +1409,12 @@
   </si>
   <si>
     <t>Tour de Pologne</t>
+  </si>
+  <si>
+    <t>Simon Dehairs</t>
+  </si>
+  <si>
+    <t>Marceli Bogusławski</t>
   </si>
 </sst>
 </file>
@@ -1416,9 +1422,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1549,6 +1555,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1897,7 +1909,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2273,7 +2285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M140"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -8026,12 +8038,54 @@
         <v>210</v>
       </c>
     </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B141" t="s">
+        <v>461</v>
+      </c>
+      <c r="C141" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" t="s">
+        <v>131</v>
+      </c>
+      <c r="E141" t="s">
+        <v>121</v>
+      </c>
+      <c r="F141" t="s">
+        <v>102</v>
+      </c>
+      <c r="G141" t="s">
+        <v>220</v>
+      </c>
+      <c r="H141" t="s">
+        <v>148</v>
+      </c>
+      <c r="I141" t="s">
+        <v>462</v>
+      </c>
+      <c r="J141" t="s">
+        <v>21</v>
+      </c>
+      <c r="K141" t="s">
+        <v>210</v>
+      </c>
+      <c r="L141" t="s">
+        <v>463</v>
+      </c>
+      <c r="M141" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M69">
       <sortCondition ref="A1:A20"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0D31DF0-EFA6-430A-8721-10706A911FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6466FA8-8444-44DE-9E9D-5E963C23E471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="465">
   <si>
     <t>Date</t>
   </si>
@@ -1415,6 +1415,9 @@
   </si>
   <si>
     <t>Marceli Bogusławski</t>
+  </si>
+  <si>
+    <t>Steffen De Schuyteneer</t>
   </si>
 </sst>
 </file>
@@ -2285,7 +2288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -8077,6 +8080,47 @@
       </c>
       <c r="M141" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B142" t="s">
+        <v>461</v>
+      </c>
+      <c r="C142" t="s">
+        <v>43</v>
+      </c>
+      <c r="D142" t="s">
+        <v>131</v>
+      </c>
+      <c r="E142" t="s">
+        <v>163</v>
+      </c>
+      <c r="F142" t="s">
+        <v>103</v>
+      </c>
+      <c r="G142" t="s">
+        <v>129</v>
+      </c>
+      <c r="H142" t="s">
+        <v>148</v>
+      </c>
+      <c r="I142" t="s">
+        <v>210</v>
+      </c>
+      <c r="J142" t="s">
+        <v>133</v>
+      </c>
+      <c r="K142" t="s">
+        <v>464</v>
+      </c>
+      <c r="L142" t="s">
+        <v>21</v>
+      </c>
+      <c r="M142" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6466FA8-8444-44DE-9E9D-5E963C23E471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AB64FC9-F016-4600-8AC0-53AC440B1DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="467">
   <si>
     <t>Date</t>
   </si>
@@ -1418,6 +1418,12 @@
   </si>
   <si>
     <t>Steffen De Schuyteneer</t>
+  </si>
+  <si>
+    <t>Louis Barré</t>
+  </si>
+  <si>
+    <t>Aaron Dockx</t>
   </si>
 </sst>
 </file>
@@ -2288,7 +2294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -8121,6 +8127,47 @@
       </c>
       <c r="M142" t="s">
         <v>360</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B143" t="s">
+        <v>461</v>
+      </c>
+      <c r="C143" t="s">
+        <v>51</v>
+      </c>
+      <c r="D143" t="s">
+        <v>435</v>
+      </c>
+      <c r="E143" t="s">
+        <v>192</v>
+      </c>
+      <c r="F143" t="s">
+        <v>296</v>
+      </c>
+      <c r="G143" t="s">
+        <v>42</v>
+      </c>
+      <c r="H143" t="s">
+        <v>465</v>
+      </c>
+      <c r="I143" t="s">
+        <v>387</v>
+      </c>
+      <c r="J143" t="s">
+        <v>190</v>
+      </c>
+      <c r="K143" t="s">
+        <v>48</v>
+      </c>
+      <c r="L143" t="s">
+        <v>466</v>
+      </c>
+      <c r="M143" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AB64FC9-F016-4600-8AC0-53AC440B1DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BB1A359-7B74-44F0-8155-B37E846D8A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="471">
   <si>
     <t>Date</t>
   </si>
@@ -1424,6 +1424,18 @@
   </si>
   <si>
     <t>Aaron Dockx</t>
+  </si>
+  <si>
+    <t>Fabio Christen</t>
+  </si>
+  <si>
+    <t>Maximilian Schachmann</t>
+  </si>
+  <si>
+    <t>Callum Thornley</t>
+  </si>
+  <si>
+    <t>Arthur Kluckers</t>
   </si>
 </sst>
 </file>
@@ -2294,7 +2306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -8168,6 +8180,129 @@
       </c>
       <c r="M143" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B144" t="s">
+        <v>461</v>
+      </c>
+      <c r="C144" t="s">
+        <v>55</v>
+      </c>
+      <c r="D144" t="s">
+        <v>178</v>
+      </c>
+      <c r="E144" t="s">
+        <v>42</v>
+      </c>
+      <c r="F144" t="s">
+        <v>465</v>
+      </c>
+      <c r="G144" t="s">
+        <v>296</v>
+      </c>
+      <c r="H144" t="s">
+        <v>190</v>
+      </c>
+      <c r="I144" t="s">
+        <v>467</v>
+      </c>
+      <c r="J144" t="s">
+        <v>48</v>
+      </c>
+      <c r="K144" t="s">
+        <v>387</v>
+      </c>
+      <c r="L144" t="s">
+        <v>192</v>
+      </c>
+      <c r="M144" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>46242</v>
+      </c>
+      <c r="B145" t="s">
+        <v>461</v>
+      </c>
+      <c r="C145" t="s">
+        <v>158</v>
+      </c>
+      <c r="D145" t="s">
+        <v>465</v>
+      </c>
+      <c r="E145" t="s">
+        <v>192</v>
+      </c>
+      <c r="F145" t="s">
+        <v>42</v>
+      </c>
+      <c r="G145" t="s">
+        <v>395</v>
+      </c>
+      <c r="H145" t="s">
+        <v>296</v>
+      </c>
+      <c r="I145" t="s">
+        <v>190</v>
+      </c>
+      <c r="J145" t="s">
+        <v>468</v>
+      </c>
+      <c r="K145" t="s">
+        <v>48</v>
+      </c>
+      <c r="L145" t="s">
+        <v>36</v>
+      </c>
+      <c r="M145" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B146" t="s">
+        <v>461</v>
+      </c>
+      <c r="C146" t="s">
+        <v>166</v>
+      </c>
+      <c r="D146" t="s">
+        <v>155</v>
+      </c>
+      <c r="E146" t="s">
+        <v>48</v>
+      </c>
+      <c r="F146" t="s">
+        <v>469</v>
+      </c>
+      <c r="G146" t="s">
+        <v>82</v>
+      </c>
+      <c r="H146" t="s">
+        <v>78</v>
+      </c>
+      <c r="I146" t="s">
+        <v>470</v>
+      </c>
+      <c r="J146" t="s">
+        <v>42</v>
+      </c>
+      <c r="K146" t="s">
+        <v>110</v>
+      </c>
+      <c r="L146" t="s">
+        <v>113</v>
+      </c>
+      <c r="M146" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BB1A359-7B74-44F0-8155-B37E846D8A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6B8A07E-D671-4D8A-AD8E-01CF9A51B12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="473">
   <si>
     <t>Date</t>
   </si>
@@ -1436,6 +1436,12 @@
   </si>
   <si>
     <t>Arthur Kluckers</t>
+  </si>
+  <si>
+    <t>ADAC Cyclassics</t>
+  </si>
+  <si>
+    <t>Søren Wærenskjold</t>
   </si>
 </sst>
 </file>
@@ -2306,20 +2312,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M146"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M147"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2360,7 +2366,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2401,7 +2407,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2442,7 +2448,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2483,7 +2489,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2524,7 +2530,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2565,7 +2571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2606,7 +2612,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2647,7 +2653,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2688,7 +2694,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2729,7 +2735,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2770,7 +2776,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2811,7 +2817,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2852,7 +2858,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2893,7 +2899,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2934,7 +2940,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2975,7 +2981,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -3016,7 +3022,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -3057,7 +3063,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -3098,7 +3104,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -3139,7 +3145,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -3180,7 +3186,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -3221,7 +3227,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -3262,7 +3268,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -3303,7 +3309,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3344,7 +3350,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3385,7 +3391,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3426,7 +3432,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3467,7 +3473,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3508,7 +3514,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3549,7 +3555,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3590,7 +3596,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3631,7 +3637,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3672,7 +3678,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3713,7 +3719,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3754,7 +3760,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3795,7 +3801,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3836,7 +3842,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3877,7 +3883,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3918,7 +3924,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3959,7 +3965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -4000,7 +4006,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -4041,7 +4047,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -4082,7 +4088,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -4123,7 +4129,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -4164,7 +4170,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -4205,7 +4211,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -4246,7 +4252,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -4287,7 +4293,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4328,7 +4334,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4369,7 +4375,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4410,7 +4416,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4451,7 +4457,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4492,7 +4498,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4533,7 +4539,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4574,7 +4580,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4615,7 +4621,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4656,7 +4662,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4697,7 +4703,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4738,7 +4744,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4779,7 +4785,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4820,7 +4826,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4861,7 +4867,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4902,7 +4908,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4943,7 +4949,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4984,7 +4990,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -5025,7 +5031,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -5066,7 +5072,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -5107,7 +5113,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -5148,7 +5154,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -5189,7 +5195,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -5230,7 +5236,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -5271,7 +5277,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -5312,7 +5318,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5353,7 +5359,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5394,7 +5400,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5435,7 +5441,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5476,7 +5482,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5517,7 +5523,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5558,7 +5564,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5599,7 +5605,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5640,7 +5646,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5681,7 +5687,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5722,7 +5728,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5763,7 +5769,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5804,7 +5810,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5845,7 +5851,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5886,7 +5892,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5927,7 +5933,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5968,7 +5974,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -6009,7 +6015,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -6050,7 +6056,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -6091,7 +6097,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -6132,7 +6138,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -6173,7 +6179,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -6214,7 +6220,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -6255,7 +6261,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -6296,7 +6302,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6337,7 +6343,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6378,7 +6384,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6419,7 +6425,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6460,7 +6466,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6501,7 +6507,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6542,7 +6548,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6583,7 +6589,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6624,7 +6630,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6665,7 +6671,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6706,7 +6712,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6747,7 +6753,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6788,7 +6794,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6829,7 +6835,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6870,7 +6876,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6911,7 +6917,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6952,7 +6958,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6993,7 +6999,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -7034,7 +7040,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -7075,7 +7081,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -7116,7 +7122,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -7157,7 +7163,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -7198,7 +7204,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -7239,7 +7245,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -7280,7 +7286,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -7321,7 +7327,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -7362,7 +7368,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -7403,7 +7409,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -7444,7 +7450,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -7485,7 +7491,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>46217</v>
       </c>
@@ -7526,7 +7532,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>46218</v>
       </c>
@@ -7567,7 +7573,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>46219</v>
       </c>
@@ -7608,7 +7614,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>46220</v>
       </c>
@@ -7649,7 +7655,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>46221</v>
       </c>
@@ -7690,7 +7696,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>46222</v>
       </c>
@@ -7731,7 +7737,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>46224</v>
       </c>
@@ -7772,7 +7778,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>46225</v>
       </c>
@@ -7813,7 +7819,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>46226</v>
       </c>
@@ -7854,7 +7860,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>46227</v>
       </c>
@@ -7895,7 +7901,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>46228</v>
       </c>
@@ -7936,7 +7942,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>46229</v>
       </c>
@@ -7977,7 +7983,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
@@ -8018,7 +8024,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>46237</v>
       </c>
@@ -8059,7 +8065,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>46238</v>
       </c>
@@ -8100,7 +8106,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>46239</v>
       </c>
@@ -8141,7 +8147,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>46240</v>
       </c>
@@ -8182,7 +8188,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>46241</v>
       </c>
@@ -8223,7 +8229,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>46242</v>
       </c>
@@ -8264,7 +8270,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>46243</v>
       </c>
@@ -8303,6 +8309,47 @@
       </c>
       <c r="M146" t="s">
         <v>378</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B147" t="s">
+        <v>471</v>
+      </c>
+      <c r="C147" t="s">
+        <v>60</v>
+      </c>
+      <c r="D147" t="s">
+        <v>121</v>
+      </c>
+      <c r="E147" t="s">
+        <v>199</v>
+      </c>
+      <c r="F147" t="s">
+        <v>17</v>
+      </c>
+      <c r="G147" t="s">
+        <v>252</v>
+      </c>
+      <c r="H147" t="s">
+        <v>260</v>
+      </c>
+      <c r="I147" t="s">
+        <v>209</v>
+      </c>
+      <c r="J147" t="s">
+        <v>163</v>
+      </c>
+      <c r="K147" t="s">
+        <v>472</v>
+      </c>
+      <c r="L147" t="s">
+        <v>447</v>
+      </c>
+      <c r="M147" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6B8A07E-D671-4D8A-AD8E-01CF9A51B12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E51291F6-32BD-425B-A1F2-FD6D47D7D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="477">
   <si>
     <t>Date</t>
   </si>
@@ -1442,6 +1442,18 @@
   </si>
   <si>
     <t>Søren Wærenskjold</t>
+  </si>
+  <si>
+    <t>Lidl Deutschland Tour</t>
+  </si>
+  <si>
+    <t>Isaac Del Toro</t>
+  </si>
+  <si>
+    <t>Marco Haller</t>
+  </si>
+  <si>
+    <t>Tibor Del Grosso</t>
   </si>
 </sst>
 </file>
@@ -1451,7 +1463,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1588,6 +1600,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1934,9 +1953,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2312,20 +2332,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M147"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M148"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2366,7 +2386,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2407,7 +2427,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2448,7 +2468,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2489,7 +2509,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2530,7 +2550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2571,7 +2591,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2612,7 +2632,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2653,7 +2673,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2694,7 +2714,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2735,7 +2755,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2776,7 +2796,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2817,7 +2837,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2858,7 +2878,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2899,7 +2919,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2940,7 +2960,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2981,7 +3001,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -3022,7 +3042,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -3063,7 +3083,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -3104,7 +3124,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -3145,7 +3165,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -3186,7 +3206,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -3227,7 +3247,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -3268,7 +3288,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -3309,7 +3329,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3350,7 +3370,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3391,7 +3411,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3432,7 +3452,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3473,7 +3493,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3514,7 +3534,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3555,7 +3575,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3596,7 +3616,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3637,7 +3657,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3678,7 +3698,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3719,7 +3739,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3760,7 +3780,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3801,7 +3821,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3842,7 +3862,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3883,7 +3903,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3924,7 +3944,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3965,7 +3985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -4006,7 +4026,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -4047,7 +4067,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -4088,7 +4108,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -4129,7 +4149,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -4170,7 +4190,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -4211,7 +4231,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -4252,7 +4272,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -4293,7 +4313,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4334,7 +4354,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4375,7 +4395,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4416,7 +4436,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4457,7 +4477,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4498,7 +4518,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4539,7 +4559,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4580,7 +4600,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4621,7 +4641,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4662,7 +4682,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4703,7 +4723,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4744,7 +4764,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4785,7 +4805,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4826,7 +4846,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4867,7 +4887,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4908,7 +4928,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4949,7 +4969,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4990,7 +5010,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -5031,7 +5051,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -5072,7 +5092,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -5113,7 +5133,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -5154,7 +5174,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -5195,7 +5215,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -5236,7 +5256,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -5277,7 +5297,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -5318,7 +5338,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5359,7 +5379,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5400,7 +5420,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5441,7 +5461,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5482,7 +5502,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5523,7 +5543,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5564,7 +5584,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5605,7 +5625,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5646,7 +5666,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5687,7 +5707,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5728,7 +5748,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5769,7 +5789,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5810,7 +5830,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5851,7 +5871,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5892,7 +5912,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5933,7 +5953,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5974,7 +5994,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -6015,7 +6035,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -6056,7 +6076,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -6097,7 +6117,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -6138,7 +6158,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -6179,7 +6199,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -6220,7 +6240,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -6261,7 +6281,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -6302,7 +6322,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6343,7 +6363,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6384,7 +6404,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6425,7 +6445,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6466,7 +6486,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6507,7 +6527,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6548,7 +6568,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6589,7 +6609,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6630,7 +6650,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6671,7 +6691,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6712,7 +6732,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6753,7 +6773,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6794,7 +6814,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6835,7 +6855,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6876,7 +6896,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6917,7 +6937,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6958,7 +6978,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6999,7 +7019,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -7040,7 +7060,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -7081,7 +7101,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -7122,7 +7142,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -7163,7 +7183,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -7204,7 +7224,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -7245,7 +7265,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -7286,7 +7306,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -7327,7 +7347,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -7368,7 +7388,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -7409,7 +7429,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -7450,7 +7470,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -7491,7 +7511,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>46217</v>
       </c>
@@ -7532,7 +7552,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>46218</v>
       </c>
@@ -7573,7 +7593,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>46219</v>
       </c>
@@ -7614,7 +7634,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>46220</v>
       </c>
@@ -7655,7 +7675,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>46221</v>
       </c>
@@ -7696,7 +7716,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>46222</v>
       </c>
@@ -7737,7 +7757,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>46224</v>
       </c>
@@ -7778,7 +7798,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>46225</v>
       </c>
@@ -7819,7 +7839,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>46226</v>
       </c>
@@ -7860,7 +7880,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>46227</v>
       </c>
@@ -7901,7 +7921,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>46228</v>
       </c>
@@ -7942,7 +7962,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>46229</v>
       </c>
@@ -7983,7 +8003,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
@@ -8024,7 +8044,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>46237</v>
       </c>
@@ -8065,7 +8085,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>46238</v>
       </c>
@@ -8106,7 +8126,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>46239</v>
       </c>
@@ -8147,7 +8167,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>46240</v>
       </c>
@@ -8188,7 +8208,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>46241</v>
       </c>
@@ -8229,7 +8249,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>46242</v>
       </c>
@@ -8270,7 +8290,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>46243</v>
       </c>
@@ -8311,7 +8331,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>46250</v>
       </c>
@@ -8350,6 +8370,47 @@
       </c>
       <c r="M147" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C148" t="s">
+        <v>14</v>
+      </c>
+      <c r="D148" t="s">
+        <v>474</v>
+      </c>
+      <c r="E148" t="s">
+        <v>121</v>
+      </c>
+      <c r="F148" t="s">
+        <v>200</v>
+      </c>
+      <c r="G148" t="s">
+        <v>475</v>
+      </c>
+      <c r="H148" t="s">
+        <v>54</v>
+      </c>
+      <c r="I148" t="s">
+        <v>417</v>
+      </c>
+      <c r="J148" t="s">
+        <v>253</v>
+      </c>
+      <c r="K148" t="s">
+        <v>218</v>
+      </c>
+      <c r="L148" t="s">
+        <v>476</v>
+      </c>
+      <c r="M148" t="s">
+        <v>410</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E51291F6-32BD-425B-A1F2-FD6D47D7D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{E51291F6-32BD-425B-A1F2-FD6D47D7D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E17D2473-BB5D-473E-84A0-5E3914F48C58}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="479">
   <si>
     <t>Date</t>
   </si>
@@ -1454,6 +1454,12 @@
   </si>
   <si>
     <t>Tibor Del Grosso</t>
+  </si>
+  <si>
+    <t>Sam Bennett</t>
+  </si>
+  <si>
+    <t>Renewi Tour</t>
   </si>
 </sst>
 </file>
@@ -2332,7 +2338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -8411,6 +8417,47 @@
       </c>
       <c r="M148" t="s">
         <v>410</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B149" t="s">
+        <v>478</v>
+      </c>
+      <c r="C149" t="s">
+        <v>25</v>
+      </c>
+      <c r="D149" t="s">
+        <v>131</v>
+      </c>
+      <c r="E149" t="s">
+        <v>446</v>
+      </c>
+      <c r="F149" t="s">
+        <v>302</v>
+      </c>
+      <c r="G149" t="s">
+        <v>124</v>
+      </c>
+      <c r="H149" t="s">
+        <v>477</v>
+      </c>
+      <c r="I149" t="s">
+        <v>28</v>
+      </c>
+      <c r="J149" t="s">
+        <v>123</v>
+      </c>
+      <c r="K149" t="s">
+        <v>268</v>
+      </c>
+      <c r="L149" t="s">
+        <v>449</v>
+      </c>
+      <c r="M149" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{E51291F6-32BD-425B-A1F2-FD6D47D7D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E17D2473-BB5D-473E-84A0-5E3914F48C58}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{E51291F6-32BD-425B-A1F2-FD6D47D7D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76684C90-3392-4D08-AF52-ADEE037464E1}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="486">
   <si>
     <t>Date</t>
   </si>
@@ -1460,6 +1460,27 @@
   </si>
   <si>
     <t>Renewi Tour</t>
+  </si>
+  <si>
+    <t>Joshua Giddings</t>
+  </si>
+  <si>
+    <t>Jenno Berckmoes</t>
+  </si>
+  <si>
+    <t>Pepijn Reinderink</t>
+  </si>
+  <si>
+    <t>Tijmen Graat</t>
+  </si>
+  <si>
+    <t>Mathieu Burgaudeau</t>
+  </si>
+  <si>
+    <t>Alessio Magagnotti</t>
+  </si>
+  <si>
+    <t>Iúri Leitão</t>
   </si>
 </sst>
 </file>
@@ -2338,7 +2359,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M149"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -8460,9 +8481,173 @@
         <v>125</v>
       </c>
     </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B150" t="s">
+        <v>478</v>
+      </c>
+      <c r="C150" t="s">
+        <v>34</v>
+      </c>
+      <c r="D150" t="s">
+        <v>124</v>
+      </c>
+      <c r="E150" t="s">
+        <v>479</v>
+      </c>
+      <c r="F150" t="s">
+        <v>472</v>
+      </c>
+      <c r="G150" t="s">
+        <v>132</v>
+      </c>
+      <c r="H150" t="s">
+        <v>409</v>
+      </c>
+      <c r="I150" t="s">
+        <v>65</v>
+      </c>
+      <c r="J150" t="s">
+        <v>47</v>
+      </c>
+      <c r="K150" t="s">
+        <v>447</v>
+      </c>
+      <c r="L150" t="s">
+        <v>477</v>
+      </c>
+      <c r="M150" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C151" t="s">
+        <v>25</v>
+      </c>
+      <c r="D151" t="s">
+        <v>465</v>
+      </c>
+      <c r="E151" t="s">
+        <v>474</v>
+      </c>
+      <c r="F151" t="s">
+        <v>218</v>
+      </c>
+      <c r="G151" t="s">
+        <v>38</v>
+      </c>
+      <c r="H151" t="s">
+        <v>53</v>
+      </c>
+      <c r="I151" t="s">
+        <v>435</v>
+      </c>
+      <c r="J151" t="s">
+        <v>460</v>
+      </c>
+      <c r="K151" t="s">
+        <v>482</v>
+      </c>
+      <c r="L151" t="s">
+        <v>483</v>
+      </c>
+      <c r="M151" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B152" t="s">
+        <v>478</v>
+      </c>
+      <c r="C152" t="s">
+        <v>43</v>
+      </c>
+      <c r="D152" t="s">
+        <v>480</v>
+      </c>
+      <c r="E152" t="s">
+        <v>124</v>
+      </c>
+      <c r="F152" t="s">
+        <v>446</v>
+      </c>
+      <c r="G152" t="s">
+        <v>125</v>
+      </c>
+      <c r="H152" t="s">
+        <v>212</v>
+      </c>
+      <c r="I152" t="s">
+        <v>189</v>
+      </c>
+      <c r="J152" t="s">
+        <v>199</v>
+      </c>
+      <c r="K152" t="s">
+        <v>310</v>
+      </c>
+      <c r="L152" t="s">
+        <v>481</v>
+      </c>
+      <c r="M152" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C153" t="s">
+        <v>34</v>
+      </c>
+      <c r="D153" t="s">
+        <v>484</v>
+      </c>
+      <c r="E153" t="s">
+        <v>121</v>
+      </c>
+      <c r="F153" t="s">
+        <v>485</v>
+      </c>
+      <c r="G153" t="s">
+        <v>214</v>
+      </c>
+      <c r="H153" t="s">
+        <v>423</v>
+      </c>
+      <c r="I153" t="s">
+        <v>410</v>
+      </c>
+      <c r="J153" t="s">
+        <v>128</v>
+      </c>
+      <c r="K153" t="s">
+        <v>251</v>
+      </c>
+      <c r="L153" t="s">
+        <v>260</v>
+      </c>
+      <c r="M153" t="s">
+        <v>475</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M69">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M153">
       <sortCondition ref="A1:A20"/>
     </sortState>
   </autoFilter>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{E51291F6-32BD-425B-A1F2-FD6D47D7D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76684C90-3392-4D08-AF52-ADEE037464E1}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{E51291F6-32BD-425B-A1F2-FD6D47D7D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF44DA9C-FFA3-4E2A-948E-80B5C87CA6E9}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="485">
   <si>
     <t>Date</t>
   </si>
@@ -1439,9 +1439,6 @@
   </si>
   <si>
     <t>ADAC Cyclassics</t>
-  </si>
-  <si>
-    <t>Søren Wærenskjold</t>
   </si>
   <si>
     <t>Lidl Deutschland Tour</t>
@@ -8390,7 +8387,7 @@
         <v>163</v>
       </c>
       <c r="K147" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="L147" t="s">
         <v>447</v>
@@ -8404,13 +8401,13 @@
         <v>46253</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
       </c>
       <c r="D148" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E148" t="s">
         <v>121</v>
@@ -8419,7 +8416,7 @@
         <v>200</v>
       </c>
       <c r="G148" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H148" t="s">
         <v>54</v>
@@ -8434,7 +8431,7 @@
         <v>218</v>
       </c>
       <c r="L148" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M148" t="s">
         <v>410</v>
@@ -8445,7 +8442,7 @@
         <v>46253</v>
       </c>
       <c r="B149" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C149" t="s">
         <v>25</v>
@@ -8463,7 +8460,7 @@
         <v>124</v>
       </c>
       <c r="H149" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I149" t="s">
         <v>28</v>
@@ -8486,7 +8483,7 @@
         <v>46254</v>
       </c>
       <c r="B150" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C150" t="s">
         <v>34</v>
@@ -8495,10 +8492,10 @@
         <v>124</v>
       </c>
       <c r="E150" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F150" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="G150" t="s">
         <v>132</v>
@@ -8516,7 +8513,7 @@
         <v>447</v>
       </c>
       <c r="L150" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M150" t="s">
         <v>302</v>
@@ -8527,7 +8524,7 @@
         <v>46254</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C151" t="s">
         <v>25</v>
@@ -8536,7 +8533,7 @@
         <v>465</v>
       </c>
       <c r="E151" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F151" t="s">
         <v>218</v>
@@ -8554,10 +8551,10 @@
         <v>460</v>
       </c>
       <c r="K151" t="s">
+        <v>481</v>
+      </c>
+      <c r="L151" t="s">
         <v>482</v>
-      </c>
-      <c r="L151" t="s">
-        <v>483</v>
       </c>
       <c r="M151" t="s">
         <v>468</v>
@@ -8568,13 +8565,13 @@
         <v>46255</v>
       </c>
       <c r="B152" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C152" t="s">
         <v>43</v>
       </c>
       <c r="D152" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E152" t="s">
         <v>124</v>
@@ -8598,10 +8595,10 @@
         <v>310</v>
       </c>
       <c r="L152" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="M152" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.25">
@@ -8609,19 +8606,19 @@
         <v>46255</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C153" t="s">
         <v>34</v>
       </c>
       <c r="D153" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E153" t="s">
         <v>121</v>
       </c>
       <c r="F153" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G153" t="s">
         <v>214</v>
@@ -8642,7 +8639,7 @@
         <v>260</v>
       </c>
       <c r="M153" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{E51291F6-32BD-425B-A1F2-FD6D47D7D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF44DA9C-FFA3-4E2A-948E-80B5C87CA6E9}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{E51291F6-32BD-425B-A1F2-FD6D47D7D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10EE3E22-7B52-4A94-B746-AD53FF6E2C6A}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="491">
   <si>
     <t>Date</t>
   </si>
@@ -1478,6 +1478,24 @@
   </si>
   <si>
     <t>Iúri Leitão</t>
+  </si>
+  <si>
+    <t>Oscar Chamberlain</t>
+  </si>
+  <si>
+    <t>Wout Van Aert</t>
+  </si>
+  <si>
+    <t>Alessandro Borgo</t>
+  </si>
+  <si>
+    <t>Tim Van Dijke</t>
+  </si>
+  <si>
+    <t>Stefano Oldani</t>
+  </si>
+  <si>
+    <t>La Vuelta Ciclista a España</t>
   </si>
 </sst>
 </file>
@@ -2356,20 +2374,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M153"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M156"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2410,7 +2428,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2451,7 +2469,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2492,7 +2510,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2533,7 +2551,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2574,7 +2592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2615,7 +2633,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2656,7 +2674,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2697,7 +2715,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2738,7 +2756,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2779,7 +2797,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2820,7 +2838,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2861,7 +2879,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2902,7 +2920,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2943,7 +2961,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2984,7 +3002,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -3025,7 +3043,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -3066,7 +3084,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -3107,7 +3125,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -3148,7 +3166,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -3189,7 +3207,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -3230,7 +3248,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -3271,7 +3289,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -3312,7 +3330,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -3353,7 +3371,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3394,7 +3412,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3435,7 +3453,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3476,7 +3494,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3517,7 +3535,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3558,7 +3576,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3599,7 +3617,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3640,7 +3658,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3681,7 +3699,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3722,7 +3740,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3763,7 +3781,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3804,7 +3822,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3845,7 +3863,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3886,7 +3904,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3927,7 +3945,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3968,7 +3986,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -4009,7 +4027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -4050,7 +4068,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -4091,7 +4109,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -4132,7 +4150,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -4173,7 +4191,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -4214,7 +4232,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -4255,7 +4273,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -4296,7 +4314,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -4337,7 +4355,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4378,7 +4396,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4419,7 +4437,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4460,7 +4478,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4501,7 +4519,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4542,7 +4560,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4583,7 +4601,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4624,7 +4642,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4665,7 +4683,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4706,7 +4724,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4747,7 +4765,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4788,7 +4806,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4829,7 +4847,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4870,7 +4888,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4911,7 +4929,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4952,7 +4970,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4993,7 +5011,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -5034,7 +5052,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -5075,7 +5093,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -5116,7 +5134,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -5157,7 +5175,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -5198,7 +5216,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -5239,7 +5257,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -5280,7 +5298,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -5321,7 +5339,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -5362,7 +5380,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5403,7 +5421,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5444,7 +5462,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5485,7 +5503,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5526,7 +5544,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5567,7 +5585,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5608,7 +5626,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5649,7 +5667,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5690,7 +5708,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5731,7 +5749,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5772,7 +5790,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5813,7 +5831,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5854,7 +5872,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5895,7 +5913,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5936,7 +5954,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5977,7 +5995,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -6018,7 +6036,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -6059,7 +6077,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -6100,7 +6118,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -6141,7 +6159,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -6182,7 +6200,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -6223,7 +6241,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -6264,7 +6282,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -6305,7 +6323,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -6346,7 +6364,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6387,7 +6405,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6428,7 +6446,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6469,7 +6487,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6510,7 +6528,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6551,7 +6569,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6592,7 +6610,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6633,7 +6651,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6674,7 +6692,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6715,7 +6733,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6756,7 +6774,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6797,7 +6815,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6838,7 +6856,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6879,7 +6897,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6920,7 +6938,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6961,7 +6979,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -7002,7 +7020,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -7043,7 +7061,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -7084,7 +7102,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -7125,7 +7143,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -7166,7 +7184,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -7207,7 +7225,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -7248,7 +7266,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -7289,7 +7307,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -7330,7 +7348,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -7371,7 +7389,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -7412,7 +7430,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -7453,7 +7471,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -7494,7 +7512,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -7535,7 +7553,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>46217</v>
       </c>
@@ -7576,7 +7594,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>46218</v>
       </c>
@@ -7617,7 +7635,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>46219</v>
       </c>
@@ -7658,7 +7676,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>46220</v>
       </c>
@@ -7699,7 +7717,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>46221</v>
       </c>
@@ -7740,7 +7758,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>46222</v>
       </c>
@@ -7781,7 +7799,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>46224</v>
       </c>
@@ -7822,7 +7840,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>46225</v>
       </c>
@@ -7863,7 +7881,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>46226</v>
       </c>
@@ -7904,7 +7922,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>46227</v>
       </c>
@@ -7945,7 +7963,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>46228</v>
       </c>
@@ -7986,7 +8004,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>46229</v>
       </c>
@@ -8027,7 +8045,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
@@ -8068,7 +8086,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>46237</v>
       </c>
@@ -8109,7 +8127,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>46238</v>
       </c>
@@ -8150,7 +8168,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>46239</v>
       </c>
@@ -8191,7 +8209,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>46240</v>
       </c>
@@ -8232,7 +8250,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>46241</v>
       </c>
@@ -8273,7 +8291,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>46242</v>
       </c>
@@ -8314,7 +8332,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>46243</v>
       </c>
@@ -8355,7 +8373,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>46250</v>
       </c>
@@ -8396,7 +8414,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>46253</v>
       </c>
@@ -8437,7 +8455,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>46253</v>
       </c>
@@ -8478,7 +8496,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>46254</v>
       </c>
@@ -8519,7 +8537,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>46254</v>
       </c>
@@ -8560,7 +8578,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>46255</v>
       </c>
@@ -8601,7 +8619,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>46255</v>
       </c>
@@ -8640,6 +8658,129 @@
       </c>
       <c r="M153" t="s">
         <v>474</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>46256</v>
+      </c>
+      <c r="B154" t="s">
+        <v>477</v>
+      </c>
+      <c r="C154" t="s">
+        <v>51</v>
+      </c>
+      <c r="D154" t="s">
+        <v>124</v>
+      </c>
+      <c r="E154" t="s">
+        <v>446</v>
+      </c>
+      <c r="F154" t="s">
+        <v>487</v>
+      </c>
+      <c r="G154" t="s">
+        <v>268</v>
+      </c>
+      <c r="H154" t="s">
+        <v>162</v>
+      </c>
+      <c r="I154" t="s">
+        <v>438</v>
+      </c>
+      <c r="J154" t="s">
+        <v>64</v>
+      </c>
+      <c r="K154" t="s">
+        <v>488</v>
+      </c>
+      <c r="L154" t="s">
+        <v>476</v>
+      </c>
+      <c r="M154" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>46256</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C155" t="s">
+        <v>43</v>
+      </c>
+      <c r="D155" t="s">
+        <v>89</v>
+      </c>
+      <c r="E155" t="s">
+        <v>473</v>
+      </c>
+      <c r="F155" t="s">
+        <v>460</v>
+      </c>
+      <c r="G155" t="s">
+        <v>282</v>
+      </c>
+      <c r="H155" t="s">
+        <v>54</v>
+      </c>
+      <c r="I155" t="s">
+        <v>38</v>
+      </c>
+      <c r="J155" t="s">
+        <v>489</v>
+      </c>
+      <c r="K155" t="s">
+        <v>253</v>
+      </c>
+      <c r="L155" t="s">
+        <v>482</v>
+      </c>
+      <c r="M155" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>46256</v>
+      </c>
+      <c r="B156" t="s">
+        <v>490</v>
+      </c>
+      <c r="C156" t="s">
+        <v>25</v>
+      </c>
+      <c r="D156" t="s">
+        <v>202</v>
+      </c>
+      <c r="E156" t="s">
+        <v>110</v>
+      </c>
+      <c r="F156" t="s">
+        <v>108</v>
+      </c>
+      <c r="G156" t="s">
+        <v>469</v>
+      </c>
+      <c r="H156" t="s">
+        <v>173</v>
+      </c>
+      <c r="I156" t="s">
+        <v>412</v>
+      </c>
+      <c r="J156" t="s">
+        <v>485</v>
+      </c>
+      <c r="K156" t="s">
+        <v>486</v>
+      </c>
+      <c r="L156" t="s">
+        <v>48</v>
+      </c>
+      <c r="M156" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{E51291F6-32BD-425B-A1F2-FD6D47D7D9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10EE3E22-7B52-4A94-B746-AD53FF6E2C6A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDB623AB-C966-4781-886E-8722668BFCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1909" uniqueCount="494">
   <si>
     <t>Date</t>
   </si>
@@ -1496,6 +1496,15 @@
   </si>
   <si>
     <t>La Vuelta Ciclista a España</t>
+  </si>
+  <si>
+    <t>Alan Jousseaume</t>
+  </si>
+  <si>
+    <t>Kim Heiduk</t>
+  </si>
+  <si>
+    <t>Toms Skujiņš</t>
   </si>
 </sst>
 </file>
@@ -2374,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -8781,6 +8790,129 @@
       </c>
       <c r="M156" t="s">
         <v>470</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>46257</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C157" t="s">
+        <v>51</v>
+      </c>
+      <c r="D157" t="s">
+        <v>121</v>
+      </c>
+      <c r="E157" t="s">
+        <v>429</v>
+      </c>
+      <c r="F157" t="s">
+        <v>22</v>
+      </c>
+      <c r="G157" t="s">
+        <v>475</v>
+      </c>
+      <c r="H157" t="s">
+        <v>53</v>
+      </c>
+      <c r="I157" t="s">
+        <v>38</v>
+      </c>
+      <c r="J157" t="s">
+        <v>195</v>
+      </c>
+      <c r="K157" t="s">
+        <v>417</v>
+      </c>
+      <c r="L157" t="s">
+        <v>491</v>
+      </c>
+      <c r="M157" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>46257</v>
+      </c>
+      <c r="B158" t="s">
+        <v>477</v>
+      </c>
+      <c r="C158" t="s">
+        <v>55</v>
+      </c>
+      <c r="D158" t="s">
+        <v>124</v>
+      </c>
+      <c r="E158" t="s">
+        <v>162</v>
+      </c>
+      <c r="F158" t="s">
+        <v>199</v>
+      </c>
+      <c r="G158" t="s">
+        <v>310</v>
+      </c>
+      <c r="H158" t="s">
+        <v>487</v>
+      </c>
+      <c r="I158" t="s">
+        <v>479</v>
+      </c>
+      <c r="J158" t="s">
+        <v>438</v>
+      </c>
+      <c r="K158" t="s">
+        <v>67</v>
+      </c>
+      <c r="L158" t="s">
+        <v>492</v>
+      </c>
+      <c r="M158" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>46257</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C159" t="s">
+        <v>34</v>
+      </c>
+      <c r="D159" t="s">
+        <v>27</v>
+      </c>
+      <c r="E159" t="s">
+        <v>440</v>
+      </c>
+      <c r="F159" t="s">
+        <v>202</v>
+      </c>
+      <c r="G159" t="s">
+        <v>255</v>
+      </c>
+      <c r="H159" t="s">
+        <v>161</v>
+      </c>
+      <c r="I159" t="s">
+        <v>107</v>
+      </c>
+      <c r="J159" t="s">
+        <v>48</v>
+      </c>
+      <c r="K159" t="s">
+        <v>296</v>
+      </c>
+      <c r="L159" t="s">
+        <v>139</v>
+      </c>
+      <c r="M159" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDB623AB-C966-4781-886E-8722668BFCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2691FAC4-301D-488F-9036-8DFD69EF7110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1909" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="495">
   <si>
     <t>Date</t>
   </si>
@@ -1505,6 +1505,9 @@
   </si>
   <si>
     <t>Toms Skujiņš</t>
+  </si>
+  <si>
+    <t>Gregor Mühlberger</t>
   </si>
 </sst>
 </file>
@@ -2383,20 +2386,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M159"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M160"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2437,7 +2440,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2478,7 +2481,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2519,7 +2522,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2560,7 +2563,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2601,7 +2604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2642,7 +2645,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2683,7 +2686,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2724,7 +2727,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2765,7 +2768,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2806,7 +2809,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2847,7 +2850,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2888,7 +2891,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2929,7 +2932,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2970,7 +2973,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -3011,7 +3014,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -3052,7 +3055,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -3093,7 +3096,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -3134,7 +3137,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -3175,7 +3178,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -3216,7 +3219,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -3257,7 +3260,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -3298,7 +3301,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -3339,7 +3342,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -3380,7 +3383,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3421,7 +3424,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3462,7 +3465,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3503,7 +3506,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3544,7 +3547,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3585,7 +3588,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3626,7 +3629,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3667,7 +3670,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3708,7 +3711,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3749,7 +3752,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3790,7 +3793,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3831,7 +3834,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3872,7 +3875,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3913,7 +3916,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3954,7 +3957,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3995,7 +3998,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -4036,7 +4039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -4077,7 +4080,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -4118,7 +4121,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -4159,7 +4162,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -4200,7 +4203,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -4241,7 +4244,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -4282,7 +4285,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -4323,7 +4326,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -4364,7 +4367,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4405,7 +4408,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4446,7 +4449,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4487,7 +4490,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4528,7 +4531,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4569,7 +4572,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4610,7 +4613,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4651,7 +4654,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4692,7 +4695,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4733,7 +4736,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4774,7 +4777,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4815,7 +4818,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4856,7 +4859,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4897,7 +4900,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4938,7 +4941,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4979,7 +4982,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -5020,7 +5023,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -5061,7 +5064,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -5102,7 +5105,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -5143,7 +5146,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -5184,7 +5187,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -5225,7 +5228,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -5266,7 +5269,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -5307,7 +5310,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -5348,7 +5351,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -5389,7 +5392,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5430,7 +5433,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5471,7 +5474,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5512,7 +5515,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5553,7 +5556,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5594,7 +5597,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5635,7 +5638,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5676,7 +5679,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5717,7 +5720,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5758,7 +5761,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5799,7 +5802,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5840,7 +5843,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5881,7 +5884,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5922,7 +5925,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5963,7 +5966,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -6004,7 +6007,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -6045,7 +6048,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -6086,7 +6089,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -6127,7 +6130,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -6168,7 +6171,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -6209,7 +6212,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -6250,7 +6253,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -6291,7 +6294,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -6332,7 +6335,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -6373,7 +6376,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6414,7 +6417,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6455,7 +6458,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6496,7 +6499,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6537,7 +6540,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6578,7 +6581,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6619,7 +6622,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6660,7 +6663,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6701,7 +6704,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6742,7 +6745,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6783,7 +6786,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6824,7 +6827,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6865,7 +6868,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6906,7 +6909,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6947,7 +6950,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6988,7 +6991,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -7029,7 +7032,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -7070,7 +7073,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -7111,7 +7114,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -7152,7 +7155,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -7193,7 +7196,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -7234,7 +7237,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -7275,7 +7278,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -7316,7 +7319,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -7357,7 +7360,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -7398,7 +7401,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -7439,7 +7442,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -7480,7 +7483,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -7521,7 +7524,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -7562,7 +7565,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>46217</v>
       </c>
@@ -7603,7 +7606,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>46218</v>
       </c>
@@ -7644,7 +7647,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>46219</v>
       </c>
@@ -7685,7 +7688,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>46220</v>
       </c>
@@ -7726,7 +7729,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>46221</v>
       </c>
@@ -7767,7 +7770,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>46222</v>
       </c>
@@ -7808,7 +7811,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>46224</v>
       </c>
@@ -7849,7 +7852,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>46225</v>
       </c>
@@ -7890,7 +7893,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>46226</v>
       </c>
@@ -7931,7 +7934,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>46227</v>
       </c>
@@ -7972,7 +7975,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>46228</v>
       </c>
@@ -8013,7 +8016,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>46229</v>
       </c>
@@ -8054,7 +8057,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
@@ -8095,7 +8098,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>46237</v>
       </c>
@@ -8136,7 +8139,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>46238</v>
       </c>
@@ -8177,7 +8180,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>46239</v>
       </c>
@@ -8218,7 +8221,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>46240</v>
       </c>
@@ -8259,7 +8262,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>46241</v>
       </c>
@@ -8300,7 +8303,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>46242</v>
       </c>
@@ -8341,7 +8344,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>46243</v>
       </c>
@@ -8382,7 +8385,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>46250</v>
       </c>
@@ -8423,7 +8426,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>46253</v>
       </c>
@@ -8464,7 +8467,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>46253</v>
       </c>
@@ -8505,7 +8508,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>46254</v>
       </c>
@@ -8546,7 +8549,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>46254</v>
       </c>
@@ -8587,7 +8590,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>46255</v>
       </c>
@@ -8628,7 +8631,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>46255</v>
       </c>
@@ -8669,7 +8672,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>46256</v>
       </c>
@@ -8710,7 +8713,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>46256</v>
       </c>
@@ -8751,7 +8754,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>46256</v>
       </c>
@@ -8792,7 +8795,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>46257</v>
       </c>
@@ -8833,7 +8836,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>46257</v>
       </c>
@@ -8874,7 +8877,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>46257</v>
       </c>
@@ -8913,6 +8916,47 @@
       </c>
       <c r="M159" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C160" t="s">
+        <v>51</v>
+      </c>
+      <c r="D160" t="s">
+        <v>202</v>
+      </c>
+      <c r="E160" t="s">
+        <v>167</v>
+      </c>
+      <c r="F160" t="s">
+        <v>117</v>
+      </c>
+      <c r="G160" t="s">
+        <v>139</v>
+      </c>
+      <c r="H160" t="s">
+        <v>376</v>
+      </c>
+      <c r="I160" t="s">
+        <v>383</v>
+      </c>
+      <c r="J160" t="s">
+        <v>216</v>
+      </c>
+      <c r="K160" t="s">
+        <v>280</v>
+      </c>
+      <c r="L160" t="s">
+        <v>181</v>
+      </c>
+      <c r="M160" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2691FAC4-301D-488F-9036-8DFD69EF7110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CB48992-B38A-4E81-83C7-6E92E96905DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="496">
   <si>
     <t>Date</t>
   </si>
@@ -1508,6 +1508,9 @@
   </si>
   <si>
     <t>Gregor Mühlberger</t>
+  </si>
+  <si>
+    <t>Vincenzo Albanese</t>
   </si>
 </sst>
 </file>
@@ -2386,20 +2389,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M160"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M161"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2440,7 +2443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2481,7 +2484,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2522,7 +2525,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2563,7 +2566,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2604,7 +2607,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2645,7 +2648,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2686,7 +2689,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2727,7 +2730,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2768,7 +2771,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2809,7 +2812,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2850,7 +2853,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2891,7 +2894,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2932,7 +2935,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2973,7 +2976,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -3014,7 +3017,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -3055,7 +3058,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -3096,7 +3099,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -3137,7 +3140,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -3178,7 +3181,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -3219,7 +3222,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -3260,7 +3263,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -3301,7 +3304,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -3342,7 +3345,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -3383,7 +3386,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3424,7 +3427,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3465,7 +3468,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3506,7 +3509,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3547,7 +3550,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3588,7 +3591,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3629,7 +3632,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3670,7 +3673,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3711,7 +3714,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3752,7 +3755,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3793,7 +3796,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3834,7 +3837,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3875,7 +3878,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3916,7 +3919,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3957,7 +3960,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3998,7 +4001,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -4039,7 +4042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -4080,7 +4083,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -4121,7 +4124,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -4162,7 +4165,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -4203,7 +4206,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -4244,7 +4247,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -4285,7 +4288,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -4326,7 +4329,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -4367,7 +4370,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4408,7 +4411,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4449,7 +4452,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4490,7 +4493,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4531,7 +4534,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4572,7 +4575,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4613,7 +4616,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4654,7 +4657,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4695,7 +4698,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4736,7 +4739,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4777,7 +4780,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4818,7 +4821,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4859,7 +4862,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4900,7 +4903,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4941,7 +4944,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4982,7 +4985,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -5023,7 +5026,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -5064,7 +5067,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -5105,7 +5108,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -5146,7 +5149,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -5187,7 +5190,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -5228,7 +5231,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -5269,7 +5272,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -5310,7 +5313,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -5351,7 +5354,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -5392,7 +5395,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5433,7 +5436,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5474,7 +5477,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5515,7 +5518,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5556,7 +5559,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5597,7 +5600,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5638,7 +5641,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5679,7 +5682,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5720,7 +5723,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5761,7 +5764,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5802,7 +5805,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5843,7 +5846,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5884,7 +5887,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5925,7 +5928,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5966,7 +5969,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -6007,7 +6010,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -6048,7 +6051,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -6089,7 +6092,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -6130,7 +6133,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -6171,7 +6174,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -6212,7 +6215,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -6253,7 +6256,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -6294,7 +6297,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -6335,7 +6338,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -6376,7 +6379,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6417,7 +6420,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6458,7 +6461,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6499,7 +6502,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6540,7 +6543,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6581,7 +6584,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6622,7 +6625,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6663,7 +6666,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6704,7 +6707,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6745,7 +6748,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6786,7 +6789,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6827,7 +6830,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6868,7 +6871,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6909,7 +6912,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6950,7 +6953,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6991,7 +6994,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -7032,7 +7035,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -7073,7 +7076,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -7114,7 +7117,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -7155,7 +7158,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -7196,7 +7199,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -7237,7 +7240,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -7278,7 +7281,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -7319,7 +7322,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -7360,7 +7363,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -7401,7 +7404,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -7442,7 +7445,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -7483,7 +7486,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -7524,7 +7527,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -7565,7 +7568,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>46217</v>
       </c>
@@ -7606,7 +7609,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>46218</v>
       </c>
@@ -7647,7 +7650,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>46219</v>
       </c>
@@ -7688,7 +7691,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>46220</v>
       </c>
@@ -7729,7 +7732,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>46221</v>
       </c>
@@ -7770,7 +7773,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>46222</v>
       </c>
@@ -7811,7 +7814,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>46224</v>
       </c>
@@ -7852,7 +7855,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>46225</v>
       </c>
@@ -7893,7 +7896,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>46226</v>
       </c>
@@ -7934,7 +7937,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>46227</v>
       </c>
@@ -7975,7 +7978,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>46228</v>
       </c>
@@ -8016,7 +8019,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>46229</v>
       </c>
@@ -8057,7 +8060,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
@@ -8098,7 +8101,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>46237</v>
       </c>
@@ -8139,7 +8142,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>46238</v>
       </c>
@@ -8180,7 +8183,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>46239</v>
       </c>
@@ -8221,7 +8224,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>46240</v>
       </c>
@@ -8262,7 +8265,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>46241</v>
       </c>
@@ -8303,7 +8306,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>46242</v>
       </c>
@@ -8344,7 +8347,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>46243</v>
       </c>
@@ -8385,7 +8388,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>46250</v>
       </c>
@@ -8426,7 +8429,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>46253</v>
       </c>
@@ -8467,7 +8470,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>46253</v>
       </c>
@@ -8508,7 +8511,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>46254</v>
       </c>
@@ -8549,7 +8552,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>46254</v>
       </c>
@@ -8590,7 +8593,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>46255</v>
       </c>
@@ -8631,7 +8634,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>46255</v>
       </c>
@@ -8672,7 +8675,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>46256</v>
       </c>
@@ -8713,7 +8716,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>46256</v>
       </c>
@@ -8754,7 +8757,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>46256</v>
       </c>
@@ -8795,7 +8798,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>46257</v>
       </c>
@@ -8836,7 +8839,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>46257</v>
       </c>
@@ -8877,7 +8880,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>46257</v>
       </c>
@@ -8918,7 +8921,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>46259</v>
       </c>
@@ -8957,6 +8960,47 @@
       </c>
       <c r="M160" t="s">
         <v>494</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C161" t="s">
+        <v>55</v>
+      </c>
+      <c r="D161" t="s">
+        <v>27</v>
+      </c>
+      <c r="E161" t="s">
+        <v>122</v>
+      </c>
+      <c r="F161" t="s">
+        <v>495</v>
+      </c>
+      <c r="G161" t="s">
+        <v>103</v>
+      </c>
+      <c r="H161" t="s">
+        <v>296</v>
+      </c>
+      <c r="I161" t="s">
+        <v>173</v>
+      </c>
+      <c r="J161" t="s">
+        <v>263</v>
+      </c>
+      <c r="K161" t="s">
+        <v>207</v>
+      </c>
+      <c r="L161" t="s">
+        <v>273</v>
+      </c>
+      <c r="M161" t="s">
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CB48992-B38A-4E81-83C7-6E92E96905DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{7CB48992-B38A-4E81-83C7-6E92E96905DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8A5BD9F-3944-4E8E-8270-B03B7DC3813D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="496">
   <si>
     <t>Date</t>
   </si>
@@ -2389,7 +2389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -9001,6 +9001,47 @@
       </c>
       <c r="M161" t="s">
         <v>486</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C162" t="s">
+        <v>158</v>
+      </c>
+      <c r="D162" t="s">
+        <v>202</v>
+      </c>
+      <c r="E162" t="s">
+        <v>383</v>
+      </c>
+      <c r="F162" t="s">
+        <v>312</v>
+      </c>
+      <c r="G162" t="s">
+        <v>280</v>
+      </c>
+      <c r="H162" t="s">
+        <v>116</v>
+      </c>
+      <c r="I162" t="s">
+        <v>117</v>
+      </c>
+      <c r="J162" t="s">
+        <v>216</v>
+      </c>
+      <c r="K162" t="s">
+        <v>425</v>
+      </c>
+      <c r="L162" t="s">
+        <v>354</v>
+      </c>
+      <c r="M162" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{7CB48992-B38A-4E81-83C7-6E92E96905DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8A5BD9F-3944-4E8E-8270-B03B7DC3813D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5F11F8-4B87-4FD0-81E3-F0F228DBEA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="500">
   <si>
     <t>Date</t>
   </si>
@@ -1511,6 +1511,18 @@
   </si>
   <si>
     <t>Vincenzo Albanese</t>
+  </si>
+  <si>
+    <t>Juan Felipe Rodriguez</t>
+  </si>
+  <si>
+    <t>Iván Ramiro Sosa</t>
+  </si>
+  <si>
+    <t>Alexey Lutsenko</t>
+  </si>
+  <si>
+    <t>Eddie Dunbar</t>
   </si>
 </sst>
 </file>
@@ -2389,7 +2401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -9042,6 +9054,47 @@
       </c>
       <c r="M162" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C163" t="s">
+        <v>166</v>
+      </c>
+      <c r="D163" t="s">
+        <v>361</v>
+      </c>
+      <c r="E163" t="s">
+        <v>107</v>
+      </c>
+      <c r="F163" t="s">
+        <v>486</v>
+      </c>
+      <c r="G163" t="s">
+        <v>343</v>
+      </c>
+      <c r="H163" t="s">
+        <v>496</v>
+      </c>
+      <c r="I163" t="s">
+        <v>497</v>
+      </c>
+      <c r="J163" t="s">
+        <v>498</v>
+      </c>
+      <c r="K163" t="s">
+        <v>499</v>
+      </c>
+      <c r="L163" t="s">
+        <v>412</v>
+      </c>
+      <c r="M163" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5F11F8-4B87-4FD0-81E3-F0F228DBEA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C4D2E2-1EED-4BAD-9663-545C2A3C8107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="502">
   <si>
     <t>Date</t>
   </si>
@@ -1523,6 +1523,12 @@
   </si>
   <si>
     <t>Eddie Dunbar</t>
+  </si>
+  <si>
+    <t>Jordan Labrosse</t>
+  </si>
+  <si>
+    <t>Bastien Tronchon</t>
   </si>
 </sst>
 </file>
@@ -2401,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M164"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -9095,6 +9101,47 @@
       </c>
       <c r="M163" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>46263</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C164" t="s">
+        <v>236</v>
+      </c>
+      <c r="D164" t="s">
+        <v>233</v>
+      </c>
+      <c r="E164" t="s">
+        <v>255</v>
+      </c>
+      <c r="F164" t="s">
+        <v>122</v>
+      </c>
+      <c r="G164" t="s">
+        <v>76</v>
+      </c>
+      <c r="H164" t="s">
+        <v>500</v>
+      </c>
+      <c r="I164" t="s">
+        <v>103</v>
+      </c>
+      <c r="J164" t="s">
+        <v>501</v>
+      </c>
+      <c r="K164" t="s">
+        <v>161</v>
+      </c>
+      <c r="L164" t="s">
+        <v>208</v>
+      </c>
+      <c r="M164" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C4D2E2-1EED-4BAD-9663-545C2A3C8107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="502">
   <si>
     <t>Date</t>
   </si>
@@ -2407,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M165"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -9142,6 +9142,47 @@
       </c>
       <c r="M164" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A165" s="1">
+        <v>46264</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C165" t="s">
+        <v>375</v>
+      </c>
+      <c r="D165" t="s">
+        <v>383</v>
+      </c>
+      <c r="E165" t="s">
+        <v>139</v>
+      </c>
+      <c r="F165" t="s">
+        <v>216</v>
+      </c>
+      <c r="G165" t="s">
+        <v>117</v>
+      </c>
+      <c r="H165" t="s">
+        <v>425</v>
+      </c>
+      <c r="I165" t="s">
+        <v>181</v>
+      </c>
+      <c r="J165" t="s">
+        <v>167</v>
+      </c>
+      <c r="K165" t="s">
+        <v>116</v>
+      </c>
+      <c r="L165" t="s">
+        <v>280</v>
+      </c>
+      <c r="M165" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EDC3568-B2C6-4C5A-AE2B-F06E80AA5B1A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="505">
   <si>
     <t>Date</t>
   </si>
@@ -1529,6 +1529,15 @@
   </si>
   <si>
     <t>Bastien Tronchon</t>
+  </si>
+  <si>
+    <t>Bretagne Classic - Ouest-France</t>
+  </si>
+  <si>
+    <t>Alexander Kamp</t>
+  </si>
+  <si>
+    <t>Alexandre Delettre</t>
   </si>
 </sst>
 </file>
@@ -2407,7 +2416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M165"/>
+  <dimension ref="A1:M166"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -9183,6 +9192,47 @@
       </c>
       <c r="M165" t="s">
         <v>231</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>46264</v>
+      </c>
+      <c r="B166" t="s">
+        <v>502</v>
+      </c>
+      <c r="C166" t="s">
+        <v>60</v>
+      </c>
+      <c r="D166" t="s">
+        <v>193</v>
+      </c>
+      <c r="E166" t="s">
+        <v>503</v>
+      </c>
+      <c r="F166" t="s">
+        <v>487</v>
+      </c>
+      <c r="G166" t="s">
+        <v>94</v>
+      </c>
+      <c r="H166" t="s">
+        <v>479</v>
+      </c>
+      <c r="I166" t="s">
+        <v>190</v>
+      </c>
+      <c r="J166" t="s">
+        <v>188</v>
+      </c>
+      <c r="K166" t="s">
+        <v>450</v>
+      </c>
+      <c r="L166" t="s">
+        <v>504</v>
+      </c>
+      <c r="M166" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EDC3568-B2C6-4C5A-AE2B-F06E80AA5B1A}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F24F5C70-D116-49DD-8A11-F67BBEC0AD1D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="507">
   <si>
     <t>Date</t>
   </si>
@@ -1538,6 +1538,12 @@
   </si>
   <si>
     <t>Alexandre Delettre</t>
+  </si>
+  <si>
+    <t>Thibau Nys</t>
+  </si>
+  <si>
+    <t>Xabier Mikel Azparren</t>
   </si>
 </sst>
 </file>
@@ -2416,20 +2422,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M166"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M167"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2470,7 +2476,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2511,7 +2517,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2552,7 +2558,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2593,7 +2599,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2634,7 +2640,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2675,7 +2681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2716,7 +2722,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2757,7 +2763,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2798,7 +2804,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2839,7 +2845,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2880,7 +2886,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2921,7 +2927,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2962,7 +2968,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -3003,7 +3009,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -3044,7 +3050,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -3085,7 +3091,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -3126,7 +3132,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -3167,7 +3173,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -3208,7 +3214,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -3249,7 +3255,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -3290,7 +3296,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -3331,7 +3337,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -3372,7 +3378,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -3413,7 +3419,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3454,7 +3460,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3495,7 +3501,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3536,7 +3542,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3577,7 +3583,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3618,7 +3624,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3659,7 +3665,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3700,7 +3706,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3741,7 +3747,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3782,7 +3788,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3823,7 +3829,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3864,7 +3870,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3905,7 +3911,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3946,7 +3952,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3987,7 +3993,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -4028,7 +4034,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -4069,7 +4075,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -4110,7 +4116,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -4151,7 +4157,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -4192,7 +4198,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -4233,7 +4239,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -4274,7 +4280,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -4315,7 +4321,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -4356,7 +4362,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -4397,7 +4403,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4438,7 +4444,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4479,7 +4485,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4520,7 +4526,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4561,7 +4567,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4602,7 +4608,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4643,7 +4649,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4684,7 +4690,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4725,7 +4731,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4766,7 +4772,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4807,7 +4813,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4848,7 +4854,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4889,7 +4895,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4930,7 +4936,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4971,7 +4977,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -5012,7 +5018,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -5053,7 +5059,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -5094,7 +5100,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -5135,7 +5141,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -5176,7 +5182,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -5217,7 +5223,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -5258,7 +5264,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -5299,7 +5305,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -5340,7 +5346,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -5381,7 +5387,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -5422,7 +5428,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5463,7 +5469,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5504,7 +5510,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5545,7 +5551,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5586,7 +5592,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5627,7 +5633,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5668,7 +5674,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5709,7 +5715,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5750,7 +5756,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5791,7 +5797,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5832,7 +5838,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5873,7 +5879,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5914,7 +5920,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5955,7 +5961,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5996,7 +6002,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -6037,7 +6043,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -6078,7 +6084,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -6119,7 +6125,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -6160,7 +6166,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -6201,7 +6207,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -6242,7 +6248,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -6283,7 +6289,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -6324,7 +6330,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -6365,7 +6371,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -6406,7 +6412,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6447,7 +6453,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6488,7 +6494,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6529,7 +6535,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6570,7 +6576,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6611,7 +6617,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6652,7 +6658,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6693,7 +6699,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6734,7 +6740,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6775,7 +6781,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6816,7 +6822,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6857,7 +6863,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6898,7 +6904,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6939,7 +6945,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6980,7 +6986,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -7021,7 +7027,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -7062,7 +7068,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -7103,7 +7109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -7144,7 +7150,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -7185,7 +7191,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -7226,7 +7232,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -7267,7 +7273,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -7308,7 +7314,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -7349,7 +7355,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -7390,7 +7396,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -7431,7 +7437,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -7472,7 +7478,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -7513,7 +7519,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -7554,7 +7560,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -7595,7 +7601,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>46217</v>
       </c>
@@ -7636,7 +7642,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>46218</v>
       </c>
@@ -7677,7 +7683,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>46219</v>
       </c>
@@ -7718,7 +7724,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>46220</v>
       </c>
@@ -7759,7 +7765,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>46221</v>
       </c>
@@ -7800,7 +7806,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>46222</v>
       </c>
@@ -7841,7 +7847,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>46224</v>
       </c>
@@ -7882,7 +7888,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>46225</v>
       </c>
@@ -7923,7 +7929,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>46226</v>
       </c>
@@ -7964,7 +7970,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>46227</v>
       </c>
@@ -8005,7 +8011,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>46228</v>
       </c>
@@ -8046,7 +8052,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>46229</v>
       </c>
@@ -8087,7 +8093,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
@@ -8128,7 +8134,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>46237</v>
       </c>
@@ -8169,7 +8175,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>46238</v>
       </c>
@@ -8210,7 +8216,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>46239</v>
       </c>
@@ -8251,7 +8257,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>46240</v>
       </c>
@@ -8292,7 +8298,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>46241</v>
       </c>
@@ -8333,7 +8339,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>46242</v>
       </c>
@@ -8374,7 +8380,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>46243</v>
       </c>
@@ -8415,7 +8421,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>46250</v>
       </c>
@@ -8456,7 +8462,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>46253</v>
       </c>
@@ -8497,7 +8503,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>46253</v>
       </c>
@@ -8538,7 +8544,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>46254</v>
       </c>
@@ -8579,7 +8585,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>46254</v>
       </c>
@@ -8620,7 +8626,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>46255</v>
       </c>
@@ -8661,7 +8667,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>46255</v>
       </c>
@@ -8702,7 +8708,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>46256</v>
       </c>
@@ -8743,7 +8749,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>46256</v>
       </c>
@@ -8784,7 +8790,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>46256</v>
       </c>
@@ -8825,7 +8831,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>46257</v>
       </c>
@@ -8866,7 +8872,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>46257</v>
       </c>
@@ -8907,7 +8913,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>46257</v>
       </c>
@@ -8948,7 +8954,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>46259</v>
       </c>
@@ -8989,7 +8995,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>46260</v>
       </c>
@@ -9030,7 +9036,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>46261</v>
       </c>
@@ -9071,7 +9077,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>46262</v>
       </c>
@@ -9112,7 +9118,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>46263</v>
       </c>
@@ -9153,7 +9159,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>46264</v>
       </c>
@@ -9194,7 +9200,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>46264</v>
       </c>
@@ -9233,6 +9239,47 @@
       </c>
       <c r="M166" t="s">
         <v>217</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C167" t="s">
+        <v>377</v>
+      </c>
+      <c r="D167" t="s">
+        <v>501</v>
+      </c>
+      <c r="E167" t="s">
+        <v>86</v>
+      </c>
+      <c r="F167" t="s">
+        <v>505</v>
+      </c>
+      <c r="G167" t="s">
+        <v>486</v>
+      </c>
+      <c r="H167" t="s">
+        <v>103</v>
+      </c>
+      <c r="I167" t="s">
+        <v>506</v>
+      </c>
+      <c r="J167" t="s">
+        <v>48</v>
+      </c>
+      <c r="K167" t="s">
+        <v>208</v>
+      </c>
+      <c r="L167" t="s">
+        <v>500</v>
+      </c>
+      <c r="M167" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F24F5C70-D116-49DD-8A11-F67BBEC0AD1D}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8714F537-AB7F-41DB-9963-13BFE95F5792}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="510">
   <si>
     <t>Date</t>
   </si>
@@ -1544,6 +1544,15 @@
   </si>
   <si>
     <t>Xabier Mikel Azparren</t>
+  </si>
+  <si>
+    <t>Tour of Britain Men</t>
+  </si>
+  <si>
+    <t>Elliot Rowe</t>
+  </si>
+  <si>
+    <t>Paul Wright</t>
   </si>
 </sst>
 </file>
@@ -2422,17 +2431,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="27" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -9280,6 +9289,88 @@
       </c>
       <c r="M167" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C168" t="s">
+        <v>382</v>
+      </c>
+      <c r="D168" t="s">
+        <v>27</v>
+      </c>
+      <c r="E168" t="s">
+        <v>233</v>
+      </c>
+      <c r="F168" t="s">
+        <v>122</v>
+      </c>
+      <c r="G168" t="s">
+        <v>86</v>
+      </c>
+      <c r="H168" t="s">
+        <v>486</v>
+      </c>
+      <c r="I168" t="s">
+        <v>161</v>
+      </c>
+      <c r="J168" t="s">
+        <v>501</v>
+      </c>
+      <c r="K168" t="s">
+        <v>103</v>
+      </c>
+      <c r="L168" t="s">
+        <v>198</v>
+      </c>
+      <c r="M168" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B169" t="s">
+        <v>507</v>
+      </c>
+      <c r="C169" t="s">
+        <v>25</v>
+      </c>
+      <c r="D169" t="s">
+        <v>232</v>
+      </c>
+      <c r="E169" t="s">
+        <v>152</v>
+      </c>
+      <c r="F169" t="s">
+        <v>442</v>
+      </c>
+      <c r="G169" t="s">
+        <v>235</v>
+      </c>
+      <c r="H169" t="s">
+        <v>111</v>
+      </c>
+      <c r="I169" t="s">
+        <v>197</v>
+      </c>
+      <c r="J169" t="s">
+        <v>77</v>
+      </c>
+      <c r="K169" t="s">
+        <v>508</v>
+      </c>
+      <c r="L169" t="s">
+        <v>450</v>
+      </c>
+      <c r="M169" t="s">
+        <v>509</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -112,7 +112,7 @@
     <t>Sam Welsford</t>
   </si>
   <si>
-    <t>Danny van Poppel</t>
+    <t>Danny Van Poppel</t>
   </si>
   <si>
     <t>Liam Walsh</t>
@@ -304,7 +304,7 @@
     <t>Viktor Soenens</t>
   </si>
   <si>
-    <t>Raúl García Pierna</t>
+    <t>Raul Garcia Pierna</t>
   </si>
   <si>
     <t>Emil Herzog</t>
@@ -382,7 +382,7 @@
     <t>Derek Gee-West</t>
   </si>
   <si>
-    <t>Jørgen Nordhagen</t>
+    <t>Jorgen Nordhagen</t>
   </si>
   <si>
     <t>Volta ao Algarve em Bicicleta</t>
@@ -1387,10 +1387,10 @@
     <t>Fernando Gaviria</t>
   </si>
   <si>
-    <t>Brandon Mcnulty</t>
-  </si>
-  <si>
-    <t>Clement Braz Afonso</t>
+    <t>Brandon McNulty</t>
+  </si>
+  <si>
+    <t>Clément Braz Afonso</t>
   </si>
   <si>
     <t>Mattia Cattaneo</t>
@@ -1399,7 +1399,7 @@
     <t>Bruno Armirail</t>
   </si>
   <si>
-    <t>Matej Mohoric</t>
+    <t>Matej Mohorič</t>
   </si>
   <si>
     <t>Donostia San Sebastian Klasikoa</t>
@@ -1483,7 +1483,7 @@
     <t>Oscar Chamberlain</t>
   </si>
   <si>
-    <t>Wout Van Aert</t>
+    <t>Wout van Aert</t>
   </si>
   <si>
     <t>Alessandro Borgo</t>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8714F537-AB7F-41DB-9963-13BFE95F5792}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE9895B6-4693-4DC5-8661-060B86D53C6C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2041" uniqueCount="511">
   <si>
     <t>Date</t>
   </si>
@@ -1553,6 +1553,9 @@
   </si>
   <si>
     <t>Paul Wright</t>
+  </si>
+  <si>
+    <t>Brody McDonald</t>
   </si>
 </sst>
 </file>
@@ -2431,7 +2434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -9371,6 +9374,47 @@
       </c>
       <c r="M169" t="s">
         <v>509</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B170" t="s">
+        <v>507</v>
+      </c>
+      <c r="C170" t="s">
+        <v>34</v>
+      </c>
+      <c r="D170" t="s">
+        <v>302</v>
+      </c>
+      <c r="E170" t="s">
+        <v>446</v>
+      </c>
+      <c r="F170" t="s">
+        <v>476</v>
+      </c>
+      <c r="G170" t="s">
+        <v>165</v>
+      </c>
+      <c r="H170" t="s">
+        <v>16</v>
+      </c>
+      <c r="I170" t="s">
+        <v>105</v>
+      </c>
+      <c r="J170" t="s">
+        <v>450</v>
+      </c>
+      <c r="K170" t="s">
+        <v>197</v>
+      </c>
+      <c r="L170" t="s">
+        <v>45</v>
+      </c>
+      <c r="M170" t="s">
+        <v>510</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE9895B6-4693-4DC5-8661-060B86D53C6C}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54C06DBF-4A16-4A3C-96C3-2303B60460D7}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2041" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="512">
   <si>
     <t>Date</t>
   </si>
@@ -1556,6 +1556,9 @@
   </si>
   <si>
     <t>Brody McDonald</t>
+  </si>
+  <si>
+    <t>Urko Berrade</t>
   </si>
 </sst>
 </file>
@@ -2434,7 +2437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -9417,6 +9420,47 @@
         <v>510</v>
       </c>
     </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C171" t="s">
+        <v>385</v>
+      </c>
+      <c r="D171" t="s">
+        <v>343</v>
+      </c>
+      <c r="E171" t="s">
+        <v>511</v>
+      </c>
+      <c r="F171" t="s">
+        <v>231</v>
+      </c>
+      <c r="G171" t="s">
+        <v>498</v>
+      </c>
+      <c r="H171" t="s">
+        <v>323</v>
+      </c>
+      <c r="I171" t="s">
+        <v>383</v>
+      </c>
+      <c r="J171" t="s">
+        <v>117</v>
+      </c>
+      <c r="K171" t="s">
+        <v>216</v>
+      </c>
+      <c r="L171" t="s">
+        <v>280</v>
+      </c>
+      <c r="M171" t="s">
+        <v>494</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M20" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M153">
@@ -9425,7 +9469,7 @@
   </autoFilter>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54C06DBF-4A16-4A3C-96C3-2303B60460D7}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2736F79-3CE9-4695-B950-D4E702A74CE6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$20</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="519">
   <si>
     <t>Date</t>
   </si>
@@ -1559,6 +1572,27 @@
   </si>
   <si>
     <t>Urko Berrade</t>
+  </si>
+  <si>
+    <t>Axel Källberg</t>
+  </si>
+  <si>
+    <t>Timothy Dupont</t>
+  </si>
+  <si>
+    <t>Arne Santy</t>
+  </si>
+  <si>
+    <t>Boas Lysgaard</t>
+  </si>
+  <si>
+    <t>Axel Bouquet</t>
+  </si>
+  <si>
+    <t>Wout Van Aert</t>
+  </si>
+  <si>
+    <t>Simon Dalby</t>
   </si>
 </sst>
 </file>
@@ -2437,7 +2471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -9459,6 +9493,88 @@
       </c>
       <c r="M171" t="s">
         <v>494</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B172" t="s">
+        <v>507</v>
+      </c>
+      <c r="C172" t="s">
+        <v>43</v>
+      </c>
+      <c r="D172" t="s">
+        <v>446</v>
+      </c>
+      <c r="E172" t="s">
+        <v>302</v>
+      </c>
+      <c r="F172" t="s">
+        <v>512</v>
+      </c>
+      <c r="G172" t="s">
+        <v>513</v>
+      </c>
+      <c r="H172" t="s">
+        <v>165</v>
+      </c>
+      <c r="I172" t="s">
+        <v>514</v>
+      </c>
+      <c r="J172" t="s">
+        <v>16</v>
+      </c>
+      <c r="K172" t="s">
+        <v>515</v>
+      </c>
+      <c r="L172" t="s">
+        <v>516</v>
+      </c>
+      <c r="M172" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C173" t="s">
+        <v>386</v>
+      </c>
+      <c r="D173" t="s">
+        <v>517</v>
+      </c>
+      <c r="E173" t="s">
+        <v>227</v>
+      </c>
+      <c r="F173" t="s">
+        <v>27</v>
+      </c>
+      <c r="G173" t="s">
+        <v>167</v>
+      </c>
+      <c r="H173" t="s">
+        <v>495</v>
+      </c>
+      <c r="I173" t="s">
+        <v>48</v>
+      </c>
+      <c r="J173" t="s">
+        <v>413</v>
+      </c>
+      <c r="K173" t="s">
+        <v>412</v>
+      </c>
+      <c r="L173" t="s">
+        <v>518</v>
+      </c>
+      <c r="M173" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2736F79-3CE9-4695-B950-D4E702A74CE6}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{5BACDE5E-50C0-446A-B77A-69E2F7E78603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5342F941-08AE-49E6-B8D7-E9D772098B69}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="518">
   <si>
     <t>Date</t>
   </si>
@@ -1587,9 +1587,6 @@
   </si>
   <si>
     <t>Axel Bouquet</t>
-  </si>
-  <si>
-    <t>Wout Van Aert</t>
   </si>
   <si>
     <t>Simon Dalby</t>
@@ -9547,7 +9544,7 @@
         <v>386</v>
       </c>
       <c r="D173" t="s">
-        <v>517</v>
+        <v>205</v>
       </c>
       <c r="E173" t="s">
         <v>227</v>
@@ -9571,7 +9568,7 @@
         <v>412</v>
       </c>
       <c r="L173" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M173" t="s">
         <v>37</v>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_84B8F11FC41E955ABA0296C7F63626470C0EE476" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C02BA0E6-7772-4B1C-829C-9719C25F9902}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="519">
   <si>
     <t>Date</t>
   </si>
@@ -1589,7 +1589,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1607,6 +1607,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1632,13 +1638,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1973,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M178"/>
+  <dimension ref="A1:M179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -9250,7 +9255,7 @@
       <c r="B178" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C178" s="5" t="s">
+      <c r="C178" t="s">
         <v>399</v>
       </c>
       <c r="D178" t="s">
@@ -9282,6 +9287,47 @@
       </c>
       <c r="M178" t="s">
         <v>518</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A179" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C179" t="s">
+        <v>400</v>
+      </c>
+      <c r="D179" t="s">
+        <v>27</v>
+      </c>
+      <c r="E179" t="s">
+        <v>122</v>
+      </c>
+      <c r="F179" t="s">
+        <v>86</v>
+      </c>
+      <c r="G179" t="s">
+        <v>103</v>
+      </c>
+      <c r="H179" t="s">
+        <v>460</v>
+      </c>
+      <c r="I179" t="s">
+        <v>297</v>
+      </c>
+      <c r="J179" t="s">
+        <v>440</v>
+      </c>
+      <c r="K179" t="s">
+        <v>518</v>
+      </c>
+      <c r="L179" t="s">
+        <v>161</v>
+      </c>
+      <c r="M179" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -9290,6 +9336,7 @@
       <sortCondition ref="A1:A20"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B61BFE5F-FDC2-4282-9E4B-E50AB291107C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="519">
   <si>
     <t>Date</t>
   </si>
@@ -1978,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M179"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -9328,6 +9328,47 @@
       </c>
       <c r="M179" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A180" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C180" t="s">
+        <v>404</v>
+      </c>
+      <c r="D180" t="s">
+        <v>155</v>
+      </c>
+      <c r="E180" t="s">
+        <v>465</v>
+      </c>
+      <c r="F180" t="s">
+        <v>88</v>
+      </c>
+      <c r="G180" t="s">
+        <v>216</v>
+      </c>
+      <c r="H180" t="s">
+        <v>517</v>
+      </c>
+      <c r="I180" t="s">
+        <v>48</v>
+      </c>
+      <c r="J180" t="s">
+        <v>454</v>
+      </c>
+      <c r="K180" t="s">
+        <v>264</v>
+      </c>
+      <c r="L180" t="s">
+        <v>110</v>
+      </c>
+      <c r="M180" t="s">
+        <v>501</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B61BFE5F-FDC2-4282-9E4B-E50AB291107C}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F485E44-7C3D-4673-A5A3-40B50D956D5C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="518">
   <si>
     <t>Date</t>
   </si>
@@ -1574,9 +1574,6 @@
   </si>
   <si>
     <t>Ben Wiggins</t>
-  </si>
-  <si>
-    <t>Wout Van Aert</t>
   </si>
   <si>
     <t>César Macías</t>
@@ -9274,7 +9271,7 @@
         <v>86</v>
       </c>
       <c r="I178" t="s">
-        <v>517</v>
+        <v>205</v>
       </c>
       <c r="J178" t="s">
         <v>161</v>
@@ -9286,7 +9283,7 @@
         <v>263</v>
       </c>
       <c r="M178" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.25">
@@ -9321,7 +9318,7 @@
         <v>440</v>
       </c>
       <c r="K179" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L179" t="s">
         <v>161</v>
@@ -9353,7 +9350,7 @@
         <v>216</v>
       </c>
       <c r="H180" t="s">
-        <v>517</v>
+        <v>205</v>
       </c>
       <c r="I180" t="s">
         <v>48</v>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F485E44-7C3D-4673-A5A3-40B50D956D5C}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E7ED3BF-25D9-4FB0-A138-7BCC1CF97591}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="520">
   <si>
     <t>Date</t>
   </si>
@@ -1577,6 +1577,12 @@
   </si>
   <si>
     <t>César Macías</t>
+  </si>
+  <si>
+    <t>Grand Prix Cycliste de Québec</t>
+  </si>
+  <si>
+    <t>Sergio Samitier</t>
   </si>
 </sst>
 </file>
@@ -1975,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M180"/>
+  <dimension ref="A1:O182"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -9204,7 +9210,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>46271</v>
       </c>
@@ -9245,7 +9251,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>46273</v>
       </c>
@@ -9286,7 +9292,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>46274</v>
       </c>
@@ -9327,7 +9333,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>46275</v>
       </c>
@@ -9366,6 +9372,94 @@
       </c>
       <c r="M180" t="s">
         <v>501</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B181" t="s">
+        <v>518</v>
+      </c>
+      <c r="C181" t="s">
+        <v>60</v>
+      </c>
+      <c r="D181" t="s">
+        <v>74</v>
+      </c>
+      <c r="E181" t="s">
+        <v>218</v>
+      </c>
+      <c r="F181" t="s">
+        <v>50</v>
+      </c>
+      <c r="G181" t="s">
+        <v>204</v>
+      </c>
+      <c r="H181" t="s">
+        <v>289</v>
+      </c>
+      <c r="I181" t="s">
+        <v>439</v>
+      </c>
+      <c r="J181" t="s">
+        <v>190</v>
+      </c>
+      <c r="K181" t="s">
+        <v>180</v>
+      </c>
+      <c r="L181" t="s">
+        <v>142</v>
+      </c>
+      <c r="M181" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C182" t="s">
+        <v>405</v>
+      </c>
+      <c r="D182" t="s">
+        <v>494</v>
+      </c>
+      <c r="E182" t="s">
+        <v>231</v>
+      </c>
+      <c r="F182" t="s">
+        <v>145</v>
+      </c>
+      <c r="G182" t="s">
+        <v>506</v>
+      </c>
+      <c r="H182" t="s">
+        <v>434</v>
+      </c>
+      <c r="I182" t="s">
+        <v>362</v>
+      </c>
+      <c r="J182" t="s">
+        <v>300</v>
+      </c>
+      <c r="K182" t="s">
+        <v>343</v>
+      </c>
+      <c r="L182" t="s">
+        <v>414</v>
+      </c>
+      <c r="M182" t="s">
+        <v>519</v>
+      </c>
+      <c r="N182" t="s">
+        <v>415</v>
+      </c>
+      <c r="O182" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/annual-results.xlsx
+++ b/annual-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E7ED3BF-25D9-4FB0-A138-7BCC1CF97591}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{3CFB2CE0-9FF9-4035-A407-178AEB2296F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CE8E520-ECDF-45B0-AD72-8B2A7D70A1BB}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="522">
   <si>
     <t>Date</t>
   </si>
@@ -1583,6 +1583,12 @@
   </si>
   <si>
     <t>Sergio Samitier</t>
+  </si>
+  <si>
+    <t>Mikel Landa</t>
+  </si>
+  <si>
+    <t>Jørgen Nordhagen</t>
   </si>
 </sst>
 </file>
@@ -1981,20 +1987,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O182"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M183"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="13" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2035,7 +2041,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46042</v>
       </c>
@@ -2076,7 +2082,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46043</v>
       </c>
@@ -2117,7 +2123,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46044</v>
       </c>
@@ -2158,7 +2164,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46045</v>
       </c>
@@ -2199,7 +2205,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46046</v>
       </c>
@@ -2240,7 +2246,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46047</v>
       </c>
@@ -2281,7 +2287,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -2322,7 +2328,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46057</v>
       </c>
@@ -2363,7 +2369,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46058</v>
       </c>
@@ -2404,7 +2410,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46059</v>
       </c>
@@ -2445,7 +2451,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46060</v>
       </c>
@@ -2486,7 +2492,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46061</v>
       </c>
@@ -2527,7 +2533,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46069</v>
       </c>
@@ -2568,7 +2574,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46070</v>
       </c>
@@ -2609,7 +2615,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46071</v>
       </c>
@@ -2650,7 +2656,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46071</v>
       </c>
@@ -2691,7 +2697,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46072</v>
       </c>
@@ -2732,7 +2738,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46072</v>
       </c>
@@ -2773,7 +2779,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46073</v>
       </c>
@@ -2814,7 +2820,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46073</v>
       </c>
@@ -2855,7 +2861,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46074</v>
       </c>
@@ -2896,7 +2902,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46074</v>
       </c>
@@ -2937,7 +2943,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46075</v>
       </c>
@@ -2978,7 +2984,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46075</v>
       </c>
@@ -3019,7 +3025,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46081</v>
       </c>
@@ -3060,7 +3066,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46081</v>
       </c>
@@ -3101,7 +3107,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -3142,7 +3148,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46082</v>
       </c>
@@ -3183,7 +3189,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46088</v>
       </c>
@@ -3224,7 +3230,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46089</v>
       </c>
@@ -3265,7 +3271,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46090</v>
       </c>
@@ -3306,7 +3312,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46091</v>
       </c>
@@ -3347,7 +3353,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46092</v>
       </c>
@@ -3388,7 +3394,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46092</v>
       </c>
@@ -3429,7 +3435,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46093</v>
       </c>
@@ -3470,7 +3476,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46093</v>
       </c>
@@ -3511,7 +3517,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46094</v>
       </c>
@@ -3552,7 +3558,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46094</v>
       </c>
@@ -3593,7 +3599,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46095</v>
       </c>
@@ -3634,7 +3640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46095</v>
       </c>
@@ -3675,7 +3681,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46096</v>
       </c>
@@ -3716,7 +3722,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46096</v>
       </c>
@@ -3757,7 +3763,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46099</v>
       </c>
@@ -3798,7 +3804,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46099</v>
       </c>
@@ -3839,7 +3845,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46102</v>
       </c>
@@ -3880,7 +3886,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46104</v>
       </c>
@@ -3921,7 +3927,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46105</v>
       </c>
@@ -3962,7 +3968,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46106</v>
       </c>
@@ -4003,7 +4009,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46106</v>
       </c>
@@ -4044,7 +4050,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46107</v>
       </c>
@@ -4085,7 +4091,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46108</v>
       </c>
@@ -4126,7 +4132,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46108</v>
       </c>
@@ -4167,7 +4173,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46109</v>
       </c>
@@ -4208,7 +4214,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46110</v>
       </c>
@@ -4249,7 +4255,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46110</v>
       </c>
@@ -4290,7 +4296,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -4331,7 +4337,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46116</v>
       </c>
@@ -4372,7 +4378,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46117</v>
       </c>
@@ -4413,7 +4419,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46118</v>
       </c>
@@ -4454,7 +4460,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46119</v>
       </c>
@@ -4495,7 +4501,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46120</v>
       </c>
@@ -4536,7 +4542,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46120</v>
       </c>
@@ -4577,7 +4583,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46121</v>
       </c>
@@ -4618,7 +4624,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46122</v>
       </c>
@@ -4659,7 +4665,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46123</v>
       </c>
@@ -4700,7 +4706,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46124</v>
       </c>
@@ -4741,7 +4747,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46127</v>
       </c>
@@ -4782,7 +4788,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46131</v>
       </c>
@@ -4823,7 +4829,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46132</v>
       </c>
@@ -4864,7 +4870,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46133</v>
       </c>
@@ -4905,7 +4911,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46134</v>
       </c>
@@ -4946,7 +4952,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46134</v>
       </c>
@@ -4987,7 +4993,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46135</v>
       </c>
@@ -5028,7 +5034,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46136</v>
       </c>
@@ -5069,7 +5075,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46138</v>
       </c>
@@ -5110,7 +5116,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46140</v>
       </c>
@@ -5151,7 +5157,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46141</v>
       </c>
@@ -5192,7 +5198,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46142</v>
       </c>
@@ -5233,7 +5239,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46143</v>
       </c>
@@ -5274,7 +5280,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46143</v>
       </c>
@@ -5315,7 +5321,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46144</v>
       </c>
@@ -5356,7 +5362,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46145</v>
       </c>
@@ -5397,7 +5403,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46150</v>
       </c>
@@ -5438,7 +5444,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46151</v>
       </c>
@@ -5479,7 +5485,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46152</v>
       </c>
@@ -5520,7 +5526,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46154</v>
       </c>
@@ -5561,7 +5567,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46155</v>
       </c>
@@ -5602,7 +5608,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46156</v>
       </c>
@@ -5643,7 +5649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46157</v>
       </c>
@@ -5684,7 +5690,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46158</v>
       </c>
@@ -5725,7 +5731,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46159</v>
       </c>
@@ -5766,7 +5772,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46161</v>
       </c>
@@ -5807,7 +5813,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46162</v>
       </c>
@@ -5848,7 +5854,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46163</v>
       </c>
@@ -5889,7 +5895,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46164</v>
       </c>
@@ -5930,7 +5936,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46165</v>
       </c>
@@ -5971,7 +5977,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46166</v>
       </c>
@@ -6012,7 +6018,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46168</v>
       </c>
@@ -6053,7 +6059,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46169</v>
       </c>
@@ -6094,7 +6100,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46170</v>
       </c>
@@ -6135,7 +6141,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46171</v>
       </c>
@@ -6176,7 +6182,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46172</v>
       </c>
@@ -6217,7 +6223,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46173</v>
       </c>
@@ -6258,7 +6264,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46180</v>
       </c>
@@ -6299,7 +6305,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46180</v>
       </c>
@@ -6340,7 +6346,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46181</v>
       </c>
@@ -6381,7 +6387,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46183</v>
       </c>
@@ -6422,7 +6428,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46184</v>
       </c>
@@ -6463,7 +6469,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46185</v>
       </c>
@@ -6504,7 +6510,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46186</v>
       </c>
@@ -6545,7 +6551,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46187</v>
       </c>
@@ -6586,7 +6592,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46187</v>
       </c>
@@ -6627,7 +6633,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46190</v>
       </c>
@@ -6668,7 +6674,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>46191</v>
       </c>
@@ -6709,7 +6715,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46192</v>
       </c>
@@ -6750,7 +6756,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46193</v>
       </c>
@@ -6791,7 +6797,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46194</v>
       </c>
@@ -6832,7 +6838,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>46208</v>
       </c>
@@ -6873,7 +6879,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>46209</v>
       </c>
@@ -6914,7 +6920,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>46210</v>
       </c>
@@ -6955,7 +6961,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>46211</v>
       </c>
@@ -6996,7 +7002,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>46212</v>
       </c>
@@ -7037,7 +7043,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>46213</v>
       </c>
@@ -7078,7 +7084,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>46214</v>
       </c>
@@ -7119,7 +7125,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>46215</v>
       </c>
@@ -7160,7 +7166,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>46217</v>
       </c>
@@ -7201,7 +7207,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>46218</v>
       </c>
@@ -7242,7 +7248,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>46219</v>
       </c>
@@ -7283,7 +7289,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>46220</v>
       </c>
@@ -7324,7 +7330,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>46221</v>
       </c>
@@ -7365,7 +7371,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>46222</v>
       </c>
@@ -7406,7 +7412,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>46224</v>
       </c>
@@ -7447,7 +7453,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>46225</v>
       </c>
@@ -7488,7 +7494,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>46226</v>
       </c>
@@ -7529,7 +7535,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>46227</v>
       </c>
@@ -7570,7 +7576,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>46228</v>
       </c>
@@ -7611,7 +7617,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>46229</v>
       </c>
@@ -7652,7 +7658,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
@@ -7693,7 +7699,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>46237</v>
       </c>
@@ -7734,7 +7740,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>46238</v>
       </c>
@@ -7775,7 +7781,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>46239</v>
       </c>
@@ -7816,7 +7822,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>46240</v>
       </c>
@@ -7857,7 +7863,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>46241</v>
       </c>
@@ -7898,7 +7904,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>46242</v>
       </c>
@@ -7939,7 +7945,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>46243</v>
       </c>
@@ -7980,7 +7986,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>46250</v>
       </c>
@@ -8021,7 +8027,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>46253</v>
       </c>
@@ -8062,7 +8068,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>46253</v>
       </c>
@@ -8103,7 +8109,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>46254</v>
       </c>
@@ -8144,7 +8150,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>46254</v>
       </c>
@@ -8185,7 +8191,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>46255</v>
       </c>
@@ -8226,7 +8232,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>46255</v>
       </c>
@@ -8267,7 +8273,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>46256</v>
       </c>
@@ -8308,7 +8314,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>46256</v>
       </c>
@@ -8349,7 +8355,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>46256</v>
       </c>
@@ -8390,7 +8396,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>46257</v>
       </c>
@@ -8431,7 +8437,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>46257</v>
       </c>
@@ -8472,7 +8478,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>46257</v>
       </c>
@@ -8513,7 +8519,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>46259</v>
       </c>
@@ -8554,7 +8560,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>46260</v>
       </c>
@@ -8595,7 +8601,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>46261</v>
       </c>
@@ -8636,7 +8642,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>46262</v>
       </c>
@@ -8677,7 +8683,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>46263</v>
       </c>
@@ -8718,7 +8724,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>46264</v>
       </c>
@@ -8759,7 +8765,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>46264</v>
       </c>
@@ -8800,7 +8806,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>46266</v>
       </c>
@@ -8841,7 +8847,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>46267</v>
       </c>
@@ -8882,7 +8888,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>46267</v>
       </c>
@@ -8923,7 +8929,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>46268</v>
       </c>
@@ -8964,7 +8970,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>46268</v>
       </c>
@@ -9005,7 +9011,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>46269</v>
       </c>
@@ -9046,7 +9052,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>46269</v>
       </c>
@@ -9087,7 +9093,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>46270</v>
       </c>
@@ -9128,7 +9134,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>46271</v>
       </c>
@@ -9169,7 +9175,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>46270</v>
       </c>
@@ -9210,7 +9216,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>46271</v>
       </c>
@@ -9251,7 +9257,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>46273</v>
       </c>
@@ -9292,7 +9298,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>46274</v>
       </c>
@@ -9333,7 +9339,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>46275</v>
       </c>
@@ -9374,7 +9380,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>46276</v>
       </c>
@@ -9415,7 +9421,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>46276</v>
       </c>
@@ -9455,11 +9461,46 @@
       <c r="M182" t="s">
         <v>519</v>
       </c>
-      <c r="N182" t="s">
-        <v>415</v>
-      </c>
-      <c r="O182" t="s">
-        <v>117</v>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>46277</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C183" t="s">
+        <v>406</v>
+      </c>
+      <c r="D183" t="s">
+        <v>520</v>
+      </c>
+      <c r="E183" t="s">
+        <v>107</v>
+      </c>
+      <c r="F183" t="s">
+        <v>313</v>
+      </c>
+      <c r="G183" t="s">
+        <v>440</v>
+      </c>
+      <c r="H183" t="s">
+        <v>506</v>
+      </c>
+      <c r="I183" t="s">
+        <v>394</v>
+      </c>
+      <c r="J183" t="s">
+        <v>521</v>
+      </c>
+      <c r="K183" t="s">
+        <v>377</v>
+      </c>
+      <c r="L183" t="s">
+        <v>513</v>
+      </c>
+      <c r="M183" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
